--- a/baseline/data_processing_elements-MSN.xlsx
+++ b/baseline/data_processing_elements-MSN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\MSN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA902F6-5797-4499-8899-20E6BD74589B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E0253F-D8C7-41E9-8CA3-CB21A7DDB1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22210" yWindow="3130" windowWidth="13230" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSN" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="746">
   <si>
     <t>index</t>
   </si>
@@ -110,9 +110,6 @@
   </si>
   <si>
     <t>validation_comment</t>
-  </si>
-  <si>
-    <t>response_from_cohort_step1</t>
   </si>
   <si>
     <t>response_to_cohort_step1</t>
@@ -1602,16 +1599,6 @@
   </si>
   <si>
     <t>N_CVD</t>
-  </si>
-  <si>
-    <t>History of cardiovascular disease;
-Hypertension</t>
-  </si>
-  <si>
-    <t>0 = No history of CVD, 
-1 = History of CVD; 
--999 = missing;
-Hypertension (yes/no) was based on the average blood pressure and antihypertensive medication use. Participants were considered to have hypertension when the average systolic blood pressure ≥ 140 mmHg, or when the diastolic blood pressure ≥90, or when they used antihypertensive medication</t>
   </si>
   <si>
     <t>case_when(N_CVD == 1 ~ 1L;
@@ -2403,10 +2390,6 @@
 Did not include walking in this variable.</t>
   </si>
   <si>
-    <t>Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
-A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
-  </si>
-  <si>
     <t>activity_Q04_done ; 
 activity_Q09_done ; 
 activity_Q10_done ; 
@@ -2434,11 +2417,6 @@
     <t>Based on the variables in the online data dictionary. Are all variables available and part of the input dataset?</t>
   </si>
   <si>
-    <t>case_when(
-activity_Q04_done == 1 | activity_Q09_done ==1 | activity_Q10_done == 1 | activity_Q11_done ==1 | activity_Q12_done ==1 | activity_Q14_done == 1 ~ 1L ; 
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>We received conflicting information about this variable. It was indicated as unavailable in the question sheet (2026-07-10), but in the 'BL var no information' sheet there is the comment "We have all items of the rose questionnaire". Need to confirm what is available.</t>
   </si>
   <si>
@@ -2472,9 +2450,6 @@
   </si>
   <si>
     <t>recode(1:5=0 ; 9=0 ; 6:8=1 ; 10:11=NA ; ELSE=NA)</t>
-  </si>
-  <si>
-    <t>recode(0 = "Armed Forces Occupations"; 1 = "Managers"; 2 = "Professionals"; 3 = "Technicians and Associate Professionals"; 4 = "Clerical Support Workers"; 5 = "Service and Sales Workers"; 6 = "Skilled Agricultural, Forestry and Fishery Workers"; 7 = "Craft and Related Trades Workers"; 8 = "Plant and Machine Operators and Assemblers"; 9 = "Elementary Occupations")</t>
   </si>
   <si>
     <t>case_when(
@@ -2552,6 +2527,63 @@
   </si>
   <si>
     <t>Corrected rule_category. Fixed a typo in algorithm.</t>
+  </si>
+  <si>
+    <t>Current input variable is ok.</t>
+  </si>
+  <si>
+    <t>Do have this variable, but only for the baseline. Not yet in input, but we can add.</t>
+  </si>
+  <si>
+    <t>Do have this variable, but only for the baseline. Not yet in input, but we can add.
+recode(0 = "Armed Forces Occupations"; 1 = "Managers"; 2 = "Professionals"; 3 = "Technicians and Associate Professionals"; 4 = "Clerical Support Workers"; 5 = "Service and Sales Workers"; 6 = "Skilled Agricultural, Forestry and Fishery Workers"; 7 = "Craft and Related Trades Workers"; 8 = "Plant and Machine Operators and Assemblers"; 9 = "Elementary Occupations")</t>
+  </si>
+  <si>
+    <t>Is available, but not in online data dictionary yet. Can be requested. Baseline and follow-up.</t>
+  </si>
+  <si>
+    <t>4 category variable has same information as 3 category but more detailed.</t>
+  </si>
+  <si>
+    <t>Do have this variable, for the baseline and follow-up. Not yet in input, but we can request.</t>
+  </si>
+  <si>
+    <t>Not in input dataset, would need to be requested. 
+Cannot distinguish between leisure vs other. 
+Possibly categorical. To check.
+Conditional on parent variable 'Did you walk?'</t>
+  </si>
+  <si>
+    <t>Available, need to request. 
+case_when(
+activity_Q04_done == 1 | activity_Q09_done ==1 | activity_Q10_done == 1 | activity_Q11_done ==1 | activity_Q12_done ==1 | activity_Q14_done == 1 ~ 1L ; 
+ELSE ~ NA_integer_)
+Study-specific variables are about activities "in a typical week during the past 4 weeks". Activities included were: fast cycling, jogging, swimming, tennis, teamsport, and heavy exercise. Walking, slow cycling, and light exercise were not included.
+A positive response to any sport activity was coded as DataSchema category 1 = Yes. DataSchema category 0 = No could not be coded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Available in baseline and follow up, need to request. </t>
+  </si>
+  <si>
+    <t>History of cardiovascular disease</t>
+  </si>
+  <si>
+    <t>0 = No history of CVD, 
+1 = History of CVD; 
+-999 = missing</t>
+  </si>
+  <si>
+    <t>Possibly to update, when we receive other CVD variables.</t>
+  </si>
+  <si>
+    <t>response_from_cohort_step1_2026_08_06</t>
+  </si>
+  <si>
+    <t>Available, but need to request.</t>
+  </si>
+  <si>
+    <t>Available, but need to request and probably to clean. 
+To request and evaluate, but might not be compatible.</t>
   </si>
 </sst>
 </file>
@@ -3030,7 +3062,7 @@
     <col min="9" max="9" width="22.140625" style="9" customWidth="1"/>
     <col min="10" max="10" width="28.7109375" style="9" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="37" style="9" customWidth="1"/>
+    <col min="12" max="12" width="37" style="10" customWidth="1"/>
     <col min="13" max="13" width="33.5703125" style="10" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="32.7109375" style="9" customWidth="1"/>
     <col min="15" max="15" width="16.5703125" style="9" bestFit="1" customWidth="1"/>
@@ -3048,7 +3080,7 @@
     <col min="27" max="27" width="60.7109375" style="10" customWidth="1"/>
     <col min="28" max="28" width="63.140625" style="10" customWidth="1"/>
     <col min="29" max="29" width="60.7109375" style="10" customWidth="1"/>
-    <col min="30" max="30" width="27.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="64" style="9" customWidth="1"/>
     <col min="31" max="31" width="24.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="27.42578125" style="9" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="24.85546875" style="9" bestFit="1" customWidth="1"/>
@@ -3089,7 +3121,7 @@
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
@@ -3144,16 +3176,16 @@
         <v>28</v>
       </c>
       <c r="AD1" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
@@ -3161,46 +3193,46 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>36</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>37</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="T2" s="10"/>
       <c r="W2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="Y2" s="10" t="s">
-        <v>43</v>
-      </c>
       <c r="Z2" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -3208,44 +3240,44 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="F3" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="N3" s="10"/>
       <c r="T3" s="10"/>
       <c r="W3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X3" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z3" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -3253,44 +3285,44 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" s="10"/>
       <c r="T4" s="10"/>
       <c r="W4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X4" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z4" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="Z4" s="12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -3298,41 +3330,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="10"/>
       <c r="T5" s="10"/>
       <c r="W5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X5" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X5" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y5" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z5" s="11">
         <v>1</v>
@@ -3343,53 +3375,53 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="L6" s="8"/>
+      <c r="M6" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="10" t="s">
+      <c r="N6" s="10" t="s">
         <v>67</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="T6" s="10"/>
       <c r="W6" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y6" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="Z6" s="11" t="s">
+      <c r="AA6" s="10" t="s">
         <v>71</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="30" x14ac:dyDescent="0.25">
@@ -3397,48 +3429,48 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>75</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="N7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="T7" s="10" t="s">
+      <c r="W7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="W7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Z7" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="Z7" s="11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -3446,50 +3478,50 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="L8" s="8"/>
+      <c r="M8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="T8" s="10"/>
       <c r="W8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X8" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y8" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3497,52 +3529,52 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="M9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="N9" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="W9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="W9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Z9" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="Z9" s="11" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3550,55 +3582,55 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>103</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>104</v>
+      <c r="L10" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="T10" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="T10" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="W10" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3606,54 +3638,54 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>107</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="10" t="s">
+      <c r="N11" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="T11" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="T11" s="10" t="s">
+      <c r="W11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z11" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="W11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y11" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z11" s="11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3661,53 +3693,53 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>119</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="10"/>
       <c r="T12" s="10"/>
       <c r="V12" s="10" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="W12" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X12" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X12" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y12" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3715,53 +3747,53 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>124</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>126</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13" s="10"/>
       <c r="T13" s="10"/>
       <c r="V13" s="10" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="W13" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X13" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X13" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y13" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3769,53 +3801,53 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N14" s="10"/>
       <c r="T14" s="10"/>
       <c r="V14" s="10" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="W14" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X14" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X14" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y14" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3823,53 +3855,53 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>134</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>136</v>
-      </c>
       <c r="K15" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15" s="10"/>
       <c r="T15" s="10"/>
       <c r="V15" s="10" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="W15" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X15" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X15" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y15" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3877,948 +3909,960 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>141</v>
-      </c>
       <c r="K16" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="10"/>
       <c r="T16" s="10"/>
       <c r="V16" s="10" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="W16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X16" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X16" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y16" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>146</v>
-      </c>
       <c r="K17" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="10"/>
       <c r="T17" s="10"/>
       <c r="V17" s="10" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="W17" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X17" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X17" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y17" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>151</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>104</v>
+        <v>109</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" s="10"/>
       <c r="T18" s="10"/>
       <c r="V18" s="10" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="W18" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X18" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X18" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y18" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>104</v>
+      <c r="L19" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="10"/>
       <c r="T19" s="10"/>
       <c r="V19" s="10" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="W19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X19" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X19" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y19" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z19" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="150" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7" t="s">
+      <c r="M20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="N20" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="T20" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="T20" s="10" t="s">
+      <c r="V20" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="W20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z20" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="W20" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X20" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y20" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z20" s="11" t="s">
-        <v>167</v>
-      </c>
       <c r="AB20" s="14" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="21" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+      <c r="AD20" s="9" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>170</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>173</v>
-      </c>
       <c r="M21" s="14" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="T21" s="10"/>
       <c r="W21" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z21" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA21" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="X21" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y21" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z21" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="AA21" s="10" t="s">
-        <v>175</v>
-      </c>
       <c r="AB21" s="14" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+      <c r="AD21" s="9" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="L22" s="8"/>
       <c r="M22" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="10"/>
       <c r="T22" s="10"/>
       <c r="W22" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" ht="120" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>183</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
+      <c r="L23" s="8"/>
       <c r="M23" s="14" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="V23" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="W23" s="14" t="s">
-        <v>41</v>
+        <v>173</v>
       </c>
       <c r="X23" s="14" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="Y23" s="14" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="Z23" s="14" t="s">
-        <v>729</v>
+        <v>173</v>
       </c>
       <c r="AA23" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB23" s="14" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="AC23" s="10" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="24" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+      <c r="AD23" s="10" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="150" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>187</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7" t="s">
+      <c r="M24" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="T24" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="W24" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z24" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="M24" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="T24" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="W24" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X24" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z24" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>193</v>
-      </c>
       <c r="F25" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="N25" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="T25" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="V25" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="V25" s="10" t="s">
-        <v>198</v>
-      </c>
       <c r="W25" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X25" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z25" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>201</v>
-      </c>
       <c r="F26" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="L26" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="L26" s="7" t="s">
-        <v>204</v>
-      </c>
       <c r="M26" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="10"/>
       <c r="T26" s="10"/>
       <c r="W26" s="14" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="X26" s="14" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y26" s="14" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="Z26" s="14" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="AA26" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AB26" s="14" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="AC26" s="10" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+      <c r="AD26" s="9" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="L27" s="8"/>
+      <c r="M27" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="10" t="s">
+      <c r="N27" s="10" t="s">
         <v>212</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>213</v>
       </c>
       <c r="T27" s="10"/>
       <c r="W27" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X27" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X27" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y27" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z27" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>215</v>
-      </c>
       <c r="E28" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
-      <c r="L28" s="7" t="s">
-        <v>216</v>
+      <c r="L28" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="N28" s="10"/>
       <c r="T28" s="10"/>
       <c r="W28" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y28" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y28" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="Z28" s="11" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>220</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>221</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L29" s="7"/>
+      <c r="L29" s="8"/>
       <c r="M29" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="T29" s="10"/>
       <c r="W29" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X29" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y29" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z29" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>224</v>
-      </c>
       <c r="E30" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
-      <c r="L30" s="7" t="s">
-        <v>216</v>
+      <c r="L30" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N30" s="10"/>
       <c r="T30" s="10"/>
       <c r="W30" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y30" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y30" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="Z30" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>228</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L31" s="7"/>
+      <c r="L31" s="8"/>
       <c r="M31" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="N31" s="10" t="s">
         <v>230</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>231</v>
       </c>
       <c r="T31" s="10"/>
       <c r="W31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X31" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X31" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y31" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z31" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L32" s="7"/>
+      <c r="L32" s="8"/>
       <c r="M32" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="N32" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>236</v>
       </c>
       <c r="T32" s="10"/>
       <c r="V32" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="W32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X32" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z32" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="W32" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X32" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z32" s="11" t="s">
+    </row>
+    <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="7" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A33" s="9">
-        <v>32</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="7" t="s">
+      <c r="D33" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>240</v>
-      </c>
       <c r="E33" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
-      <c r="L33" s="7" t="s">
-        <v>216</v>
+      <c r="L33" s="8" t="s">
+        <v>215</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N33" s="10"/>
       <c r="T33" s="10"/>
       <c r="W33" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y33" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y33" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="Z33" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
@@ -4826,46 +4870,46 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="F34" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>244</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>245</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
+      <c r="L34" s="8"/>
       <c r="M34" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N34" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>247</v>
       </c>
       <c r="T34" s="10"/>
       <c r="W34" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X34" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X34" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y34" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z34" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -4873,44 +4917,44 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>249</v>
-      </c>
       <c r="E35" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
+      <c r="L35" s="8"/>
       <c r="M35" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="N35" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>247</v>
       </c>
       <c r="T35" s="10"/>
       <c r="W35" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X35" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y35" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="Y35" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="Z35" s="11" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -4918,55 +4962,55 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>254</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K36" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="L36" s="8"/>
+      <c r="M36" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="10" t="s">
+      <c r="N36" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="T36" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="V36" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="V36" s="9" t="s">
+      <c r="W36" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X36" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z36" s="11" t="s">
         <v>260</v>
-      </c>
-      <c r="W36" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X36" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y36" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z36" s="11" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
@@ -4974,53 +5018,53 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>264</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="K37" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="L37" s="7"/>
+      <c r="L37" s="8"/>
       <c r="M37" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="N37" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="T37" s="10"/>
       <c r="V37" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="W37" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X37" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X37" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y37" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Z37" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -5028,53 +5072,53 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>270</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>271</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K38" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="L38" s="8"/>
+      <c r="M38" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="10" t="s">
+      <c r="N38" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="T38" s="10"/>
       <c r="V38" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="W38" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X38" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z38" s="11" t="s">
         <v>275</v>
-      </c>
-      <c r="W38" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X38" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z38" s="11" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -5082,95 +5126,95 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="L39" s="8"/>
+      <c r="M39" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="10" t="s">
+      <c r="N39" s="10" t="s">
         <v>282</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>283</v>
       </c>
       <c r="T39" s="10"/>
       <c r="V39" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="W39" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X39" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z39" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="W39" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X39" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y39" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z39" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="E40" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>288</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
-      <c r="L40" s="7" t="s">
-        <v>289</v>
+      <c r="L40" s="8" t="s">
+        <v>288</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N40" s="10"/>
       <c r="T40" s="10"/>
       <c r="W40" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X40" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y40" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z40" s="11">
         <v>2</v>
@@ -5181,50 +5225,50 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="E41" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="L41" s="8"/>
       <c r="M41" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N41" s="10"/>
       <c r="T41" s="10"/>
       <c r="W41" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X41" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z41" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AC41" s="10" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
@@ -5232,46 +5276,46 @@
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C42" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="E42" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>295</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>296</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="L42" s="8"/>
       <c r="M42" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="N42" s="10" t="s">
         <v>297</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>298</v>
       </c>
       <c r="T42" s="10"/>
       <c r="W42" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X42" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X42" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y42" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z42" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
@@ -5279,46 +5323,46 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="E43" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G43" s="7" t="s">
         <v>300</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>301</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
+      <c r="L43" s="8"/>
       <c r="M43" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="N43" s="10" t="s">
         <v>302</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>303</v>
       </c>
       <c r="T43" s="10"/>
       <c r="W43" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X43" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X43" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y43" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z43" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
@@ -5326,46 +5370,46 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>305</v>
-      </c>
       <c r="E44" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
+      <c r="L44" s="8"/>
       <c r="M44" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="N44" s="10" t="s">
         <v>306</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>307</v>
       </c>
       <c r="T44" s="10"/>
       <c r="W44" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X44" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X44" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y44" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z44" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
@@ -5373,46 +5417,46 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>309</v>
-      </c>
       <c r="E45" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
+      <c r="L45" s="8"/>
       <c r="M45" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="N45" s="10" t="s">
         <v>310</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>311</v>
       </c>
       <c r="T45" s="10"/>
       <c r="W45" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X45" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X45" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y45" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z45" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -5420,51 +5464,51 @@
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>313</v>
-      </c>
       <c r="E46" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
       <c r="J46" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="K46" s="7"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="10" t="s">
+      <c r="N46" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>316</v>
       </c>
       <c r="T46" s="10"/>
       <c r="V46" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="W46" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y46" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z46" s="11" t="s">
         <v>317</v>
-      </c>
-      <c r="W46" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X46" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y46" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z46" s="11" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
@@ -5472,46 +5516,46 @@
         <v>46</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>320</v>
-      </c>
       <c r="E47" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
+      <c r="L47" s="8"/>
       <c r="M47" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="N47" s="10" t="s">
         <v>321</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>322</v>
       </c>
       <c r="T47" s="10"/>
       <c r="W47" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X47" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X47" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y47" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z47" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5519,3527 +5563,3618 @@
         <v>47</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C48" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>324</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>325</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
       <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
+      <c r="L48" s="8"/>
       <c r="M48" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="N48" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="N48" s="10" t="s">
+      <c r="T48" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="T48" s="10" t="s">
+      <c r="W48" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y48" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z48" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="W48" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X48" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y48" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z48" s="12" t="s">
+      <c r="AA48" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="AA48" s="10" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="49" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>48</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C49" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="K49" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="L49" s="8"/>
+      <c r="M49" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="L49" s="7"/>
-      <c r="M49" s="10" t="s">
+      <c r="N49" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="N49" s="10" t="s">
+      <c r="T49" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="T49" s="10" t="s">
+      <c r="W49" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X49" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y49" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z49" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="W49" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X49" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y49" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z49" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="50" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>341</v>
-      </c>
       <c r="E50" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="L50" s="7" t="s">
-        <v>343</v>
-      </c>
       <c r="M50" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N50" s="10"/>
       <c r="T50" s="10"/>
       <c r="W50" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X50" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y50" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z50" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA50" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AC50" s="10" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="51" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>346</v>
-      </c>
       <c r="E51" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="L51" s="8"/>
+      <c r="M51" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="L51" s="7"/>
-      <c r="M51" s="10" t="s">
+      <c r="N51" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="N51" s="10" t="s">
+      <c r="T51" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="W51" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X51" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y51" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z51" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="T51" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="W51" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X51" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y51" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z51" s="12" t="s">
+      <c r="AA51" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="AA51" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>51</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>354</v>
-      </c>
       <c r="E52" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="K52" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="K52" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="L52" s="7" t="s">
-        <v>343</v>
+      <c r="L52" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N52" s="10"/>
       <c r="T52" s="10"/>
       <c r="W52" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X52" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y52" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z52" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>52</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C53" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>358</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>359</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
+      <c r="L53" s="8"/>
       <c r="M53" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="N53" s="10" t="s">
+      <c r="T53" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="W53" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X53" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y53" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z53" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="T53" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="W53" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X53" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y53" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z53" s="12" t="s">
-        <v>362</v>
-      </c>
       <c r="AA53" s="10" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>53</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="E54" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="K54" s="7" t="s">
+      <c r="L54" s="8"/>
+      <c r="M54" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="L54" s="7"/>
-      <c r="M54" s="10" t="s">
+      <c r="N54" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="N54" s="10" t="s">
-        <v>369</v>
-      </c>
       <c r="T54" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="W54" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X54" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y54" s="10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Z54" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="AA54" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="AC54" s="10" t="s">
         <v>730</v>
       </c>
-      <c r="AA54" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="AC54" s="10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>54</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>371</v>
-      </c>
       <c r="E55" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
       <c r="I55" s="7"/>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
-      <c r="L55" s="7" t="s">
+      <c r="L55" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="M55" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="N55" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="T55" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="V55" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="W55" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X55" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y55" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z55" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA55" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>699</v>
-      </c>
-      <c r="T55" s="10" t="s">
-        <v>700</v>
-      </c>
-      <c r="V55" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="W55" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X55" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y55" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z55" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>374</v>
-      </c>
       <c r="AC55" s="10" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>55</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>376</v>
-      </c>
       <c r="E56" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="K56" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="L56" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="L56" s="7" t="s">
+      <c r="M56" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="N56" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="N56" s="10" t="s">
+      <c r="T56" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="T56" s="10" t="s">
+      <c r="W56" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X56" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y56" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z56" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="W56" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X56" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y56" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z56" s="11" t="s">
-        <v>383</v>
-      </c>
       <c r="AB56" s="14" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+      <c r="AD56" s="9" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>56</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>385</v>
-      </c>
       <c r="E57" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="L57" s="7" t="s">
-        <v>386</v>
+        <v>377</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>385</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="T57" s="10"/>
       <c r="V57" s="10" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="W57" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="X57" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="X57" s="10" t="s">
-        <v>121</v>
-      </c>
       <c r="Y57" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z57" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA57" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC57" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="E58" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>390</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="L58" s="7"/>
+        <v>377</v>
+      </c>
+      <c r="L58" s="8"/>
       <c r="M58" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N58" s="10"/>
       <c r="T58" s="10"/>
-      <c r="W58" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X58" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y58" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z58" s="11" t="s">
-        <v>120</v>
+      <c r="W58" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X58" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y58" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z58" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB58" s="14" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="AC58" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+        <v>720</v>
+      </c>
+      <c r="AD58" s="9" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C59" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>393</v>
-      </c>
       <c r="E59" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F59" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G59" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
+      <c r="L59" s="8"/>
       <c r="M59" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N59" s="10"/>
       <c r="T59" s="10"/>
       <c r="W59" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X59" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y59" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z59" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" ht="135" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>395</v>
-      </c>
       <c r="E60" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="K60" s="7"/>
+      <c r="L60" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7" t="s">
-        <v>397</v>
-      </c>
       <c r="M60" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N60" s="10"/>
       <c r="T60" s="10"/>
       <c r="W60" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X60" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z60" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="E61" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>400</v>
-      </c>
       <c r="F61" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="L61" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="L61" s="7" t="s">
-        <v>402</v>
-      </c>
       <c r="M61" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N61" s="10"/>
       <c r="T61" s="10"/>
       <c r="W61" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X61" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y61" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z61" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="62" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>404</v>
-      </c>
       <c r="E62" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="K62" s="7"/>
+      <c r="L62" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7" t="s">
-        <v>406</v>
-      </c>
       <c r="M62" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N62" s="10"/>
       <c r="T62" s="10"/>
       <c r="W62" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X62" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y62" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z62" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C63" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>408</v>
-      </c>
       <c r="E63" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
-      <c r="L63" s="7" t="s">
-        <v>406</v>
+      <c r="L63" s="8" t="s">
+        <v>405</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N63" s="10"/>
       <c r="T63" s="10"/>
       <c r="W63" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X63" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z63" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="64" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>410</v>
-      </c>
       <c r="E64" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
-      <c r="L64" s="7" t="s">
-        <v>406</v>
+      <c r="L64" s="8" t="s">
+        <v>405</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N64" s="10"/>
       <c r="T64" s="10"/>
       <c r="W64" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X64" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y64" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z64" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:30" ht="165" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>64</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>413</v>
-      </c>
       <c r="F65" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
       <c r="I65" s="7"/>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
-      <c r="L65" s="7" t="s">
-        <v>414</v>
+      <c r="L65" s="8" t="s">
+        <v>413</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N65" s="10"/>
       <c r="T65" s="10"/>
       <c r="W65" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X65" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y65" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z65" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>65</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="E66" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>417</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="K66" s="7"/>
+      <c r="L66" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="K66" s="7"/>
-      <c r="L66" s="7" t="s">
-        <v>406</v>
-      </c>
       <c r="M66" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N66" s="10"/>
       <c r="T66" s="10"/>
       <c r="W66" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X66" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y66" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z66" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>66</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C67" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="E67" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>420</v>
-      </c>
       <c r="F67" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="K67" s="7"/>
+      <c r="L67" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="K67" s="7"/>
-      <c r="L67" s="7" t="s">
-        <v>406</v>
-      </c>
       <c r="M67" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N67" s="10"/>
       <c r="T67" s="10"/>
       <c r="W67" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X67" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z67" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>67</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>422</v>
-      </c>
       <c r="E68" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F68" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G68" s="7" t="s">
         <v>178</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>179</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K68" s="7"/>
-      <c r="L68" s="7"/>
+      <c r="L68" s="8"/>
       <c r="M68" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N68" s="10"/>
       <c r="T68" s="10"/>
       <c r="W68" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X68" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y68" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z68" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>68</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="E69" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>425</v>
-      </c>
       <c r="F69" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
       <c r="I69" s="7"/>
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
-      <c r="L69" s="7" t="s">
-        <v>426</v>
+      <c r="L69" s="8" t="s">
+        <v>425</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N69" s="10"/>
       <c r="T69" s="10"/>
       <c r="W69" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X69" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y69" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z69" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>69</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C70" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="E70" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>429</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="L70" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="L70" s="7" t="s">
+      <c r="M70" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="M70" s="14" t="s">
-        <v>432</v>
-      </c>
       <c r="N70" s="10" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="S70" s="16"/>
       <c r="T70" s="14"/>
       <c r="W70" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="X70" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Y70" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Z70" s="14" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA70" s="10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AB70" s="14" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="AC70" s="10" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+      <c r="AD70" s="10" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>70</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D71" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="E71" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="E71" s="7" t="s">
-        <v>436</v>
-      </c>
       <c r="F71" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="L71" s="7" t="s">
-        <v>437</v>
+        <v>429</v>
+      </c>
+      <c r="L71" s="8" t="s">
+        <v>436</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N71" s="10"/>
       <c r="T71" s="10"/>
       <c r="W71" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X71" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y71" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z71" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:29" ht="180" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:30" ht="180" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>71</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C72" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="E72" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>440</v>
-      </c>
       <c r="F72" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="L72" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M72" s="14" t="s">
+        <v>709</v>
+      </c>
+      <c r="N72" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="P72" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="T72" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="V72" s="14"/>
+      <c r="W72" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X72" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y72" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z72" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA72" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="K72" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="M72" s="14" t="s">
-        <v>713</v>
-      </c>
-      <c r="N72" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="P72" s="10" t="s">
-        <v>715</v>
-      </c>
-      <c r="T72" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="V72" s="14" t="s">
+      <c r="AB72" s="14" t="s">
         <v>712</v>
       </c>
-      <c r="W72" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="X72" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y72" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z72" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="AA72" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="AB72" s="14" t="s">
-        <v>716</v>
-      </c>
       <c r="AC72" s="10" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+      <c r="AD72" s="10" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="E73" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="E73" s="7" t="s">
-        <v>445</v>
-      </c>
       <c r="F73" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K73" s="7"/>
-      <c r="L73" s="7" t="s">
-        <v>104</v>
+      <c r="L73" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N73" s="10"/>
       <c r="T73" s="10"/>
       <c r="W73" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X73" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y73" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z73" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="9">
         <v>73</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C74" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="E74" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>449</v>
-      </c>
       <c r="F74" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="M74" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="K74" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="L74" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="M74" s="10" t="s">
+      <c r="N74" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="N74" s="10" t="s">
+      <c r="T74" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="W74" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X74" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y74" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z74" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="T74" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="W74" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X74" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y74" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z74" s="11" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="75" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A75" s="9">
         <v>74</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C75" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="E75" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>456</v>
-      </c>
       <c r="F75" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="K75" s="7"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="10" t="s">
+      <c r="N75" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="N75" s="10" t="s">
+      <c r="T75" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="T75" s="10" t="s">
+      <c r="W75" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X75" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y75" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="W75" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X75" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y75" s="10" t="s">
-        <v>461</v>
-      </c>
       <c r="Z75" s="11" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="AC75" s="10" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="76" spans="1:29" ht="409.5" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>75</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="E76" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="F76" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>465</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
       <c r="J76" s="7"/>
       <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
+      <c r="L76" s="8"/>
       <c r="M76" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N76" s="10"/>
       <c r="T76" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="W76" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X76" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y76" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="W76" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X76" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y76" s="10" t="s">
-        <v>461</v>
-      </c>
       <c r="Z76" s="11" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="AC76" s="10" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="77" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>76</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C77" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>467</v>
-      </c>
       <c r="E77" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="L77" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="L77" s="7" t="s">
+      <c r="M77" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="N77" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="T77" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="N77" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="T77" s="10" t="s">
+      <c r="W77" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X77" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y77" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z77" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="W77" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X77" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y77" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z77" s="11" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="78" spans="1:29" ht="150" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>77</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C78" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="E78" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>475</v>
-      </c>
       <c r="F78" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="K78" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="K78" s="7" t="s">
+      <c r="L78" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="L78" s="7" t="s">
+      <c r="M78" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="M78" s="10" t="s">
+      <c r="N78" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="T78" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="W78" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X78" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y78" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z78" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="N78" s="10" t="s">
+      <c r="AA78" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="T78" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="W78" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X78" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y78" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z78" s="11" t="s">
-        <v>482</v>
-      </c>
-      <c r="AA78" s="10" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+      <c r="AD78" s="9" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>78</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J79" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K79" s="7"/>
-      <c r="L79" s="7" t="s">
-        <v>478</v>
+      <c r="L79" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N79" s="10"/>
       <c r="T79" s="10"/>
-      <c r="W79" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X79" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y79" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z79" s="11" t="s">
-        <v>120</v>
+      <c r="W79" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X79" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y79" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z79" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AA79" s="10" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AB79" s="14" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="80" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+      <c r="AD79" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>79</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="K80" s="7"/>
+      <c r="L80" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M80" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N80" s="10" t="s">
+        <v>491</v>
+      </c>
+      <c r="T80" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="W80" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X80" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y80" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z80" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA80" s="10" t="s">
         <v>493</v>
       </c>
-      <c r="J80" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M80" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N80" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="T80" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="W80" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X80" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y80" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z80" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA80" s="10" t="s">
-        <v>496</v>
-      </c>
       <c r="AB80" s="14" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="81" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+      <c r="AD80" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>80</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="K81" s="7"/>
+      <c r="L81" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M81" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N81" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="T81" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="W81" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X81" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y81" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z81" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA81" s="10" t="s">
         <v>500</v>
       </c>
-      <c r="J81" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N81" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="T81" s="10" t="s">
-        <v>502</v>
-      </c>
-      <c r="W81" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X81" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y81" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z81" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA81" s="10" t="s">
-        <v>503</v>
-      </c>
       <c r="AB81" s="14" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="82" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+      <c r="AD81" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>81</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K82" s="7"/>
-      <c r="L82" s="7" t="s">
-        <v>478</v>
+      <c r="L82" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N82" s="9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="T82" s="15" t="s">
-        <v>495</v>
-      </c>
-      <c r="W82" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X82" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y82" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z82" s="11" t="s">
-        <v>120</v>
+        <v>492</v>
+      </c>
+      <c r="W82" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X82" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y82" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z82" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AA82" s="10" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="AB82" s="14" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+      <c r="AD82" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>82</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="K83" s="7"/>
-      <c r="L83" s="7" t="s">
-        <v>478</v>
+      <c r="L83" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N83" s="10"/>
       <c r="T83" s="10"/>
       <c r="W83" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X83" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y83" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z83" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>83</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="K84" s="7"/>
+      <c r="L84" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="T84" s="10" t="s">
         <v>517</v>
       </c>
-      <c r="J84" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M84" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="N84" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="T84" s="10" t="s">
-        <v>520</v>
-      </c>
       <c r="W84" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X84" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X84" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y84" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z84" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="85" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>84</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J85" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="K85" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="L85" s="7" t="s">
-        <v>478</v>
+        <v>523</v>
+      </c>
+      <c r="L85" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N85" s="10"/>
       <c r="T85" s="10"/>
-      <c r="W85" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X85" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y85" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z85" s="11" t="s">
-        <v>120</v>
+      <c r="W85" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X85" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y85" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z85" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB85" s="14" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="86" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="AD85" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="9">
         <v>85</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J86" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="K86" s="7"/>
+      <c r="L86" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M86" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N86" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="T86" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="W86" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X86" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y86" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z86" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA86" s="10" t="s">
         <v>530</v>
       </c>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M86" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N86" s="10" t="s">
-        <v>531</v>
-      </c>
-      <c r="T86" s="10" t="s">
-        <v>532</v>
-      </c>
-      <c r="W86" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X86" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y86" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z86" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA86" s="10" t="s">
-        <v>533</v>
-      </c>
       <c r="AB86" s="14" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="87" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="AD86" s="10" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>86</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D87" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="K87" s="7"/>
+      <c r="L87" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M87" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="N87" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="T87" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M87" s="10" t="s">
+      <c r="V87" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="W87" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X87" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y87" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z87" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="T87" s="10" t="s">
-        <v>540</v>
-      </c>
-      <c r="V87" s="10" t="s">
-        <v>541</v>
-      </c>
-      <c r="W87" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X87" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y87" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z87" s="11" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="88" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:30" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>87</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="L88" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M88" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="N88" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="J88" s="7" t="s">
-        <v>537</v>
-      </c>
-      <c r="K88" s="7" t="s">
+      <c r="T88" s="10" t="s">
         <v>547</v>
       </c>
-      <c r="L88" s="8" t="s">
-        <v>478</v>
-      </c>
-      <c r="M88" s="10" t="s">
+      <c r="W88" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X88" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y88" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z88" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="N88" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="T88" s="10" t="s">
-        <v>550</v>
-      </c>
-      <c r="W88" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X88" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y88" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z88" s="11" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="89" spans="1:29" ht="105" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:30" ht="105" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>88</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="L89" s="7" t="s">
-        <v>555</v>
+        <v>551</v>
+      </c>
+      <c r="L89" s="8" t="s">
+        <v>552</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="T89" s="10" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="W89" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="X89" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Y89" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Z89" s="11" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="90" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>89</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>558</v>
+      </c>
+      <c r="L90" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N90" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="T90" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="K90" s="7" t="s">
+      <c r="W90" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X90" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y90" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z90" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA90" s="10" t="s">
         <v>561</v>
       </c>
-      <c r="L90" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="M90" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="N90" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="T90" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="W90" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X90" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y90" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z90" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA90" s="10" t="s">
-        <v>564</v>
-      </c>
       <c r="AB90" s="14" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="AD90" s="9" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>90</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K91" s="7"/>
-      <c r="L91" s="7" t="s">
-        <v>478</v>
+      <c r="L91" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N91" s="10"/>
       <c r="T91" s="10"/>
-      <c r="W91" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X91" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y91" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z91" s="11" t="s">
-        <v>120</v>
+      <c r="W91" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X91" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y91" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z91" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AA91" s="10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="AB91" s="14" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="AC91" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+      <c r="AD91" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="9">
         <v>91</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K92" s="7"/>
-      <c r="L92" s="7" t="s">
-        <v>478</v>
+      <c r="L92" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N92" s="10"/>
       <c r="T92" s="10"/>
-      <c r="W92" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X92" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y92" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z92" s="11" t="s">
-        <v>120</v>
+      <c r="W92" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X92" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y92" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z92" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB92" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD92" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="9">
         <v>92</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K93" s="7"/>
-      <c r="L93" s="7" t="s">
-        <v>478</v>
+      <c r="L93" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N93" s="10"/>
       <c r="T93" s="10"/>
-      <c r="W93" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X93" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y93" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z93" s="11" t="s">
-        <v>120</v>
+      <c r="W93" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X93" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y93" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z93" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB93" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD93" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>93</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K94" s="7"/>
-      <c r="L94" s="7" t="s">
-        <v>478</v>
+      <c r="L94" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N94" s="10"/>
       <c r="T94" s="10"/>
-      <c r="W94" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X94" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y94" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z94" s="11" t="s">
-        <v>120</v>
+      <c r="W94" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X94" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y94" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z94" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB94" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD94" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="9">
         <v>94</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K95" s="7"/>
-      <c r="L95" s="7" t="s">
-        <v>478</v>
+      <c r="L95" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N95" s="10"/>
       <c r="T95" s="10"/>
-      <c r="W95" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X95" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y95" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z95" s="11" t="s">
-        <v>120</v>
+      <c r="W95" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X95" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y95" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z95" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB95" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD95" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="9">
         <v>95</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K96" s="7"/>
-      <c r="L96" s="7" t="s">
-        <v>478</v>
+      <c r="L96" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N96" s="10"/>
       <c r="T96" s="10"/>
-      <c r="W96" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X96" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y96" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z96" s="11" t="s">
-        <v>120</v>
+      <c r="W96" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X96" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y96" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z96" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB96" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD96" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="9">
         <v>96</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K97" s="7"/>
-      <c r="L97" s="7" t="s">
-        <v>478</v>
+      <c r="L97" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N97" s="10"/>
       <c r="T97" s="10"/>
-      <c r="W97" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X97" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y97" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z97" s="11" t="s">
-        <v>120</v>
+      <c r="W97" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X97" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y97" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z97" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB97" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD97" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="9">
         <v>97</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K98" s="7"/>
-      <c r="L98" s="7" t="s">
-        <v>478</v>
+      <c r="L98" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N98" s="10"/>
       <c r="T98" s="10"/>
-      <c r="W98" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X98" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y98" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z98" s="11" t="s">
-        <v>120</v>
+      <c r="W98" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X98" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y98" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z98" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB98" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD98" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="9">
         <v>98</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K99" s="7"/>
-      <c r="L99" s="7" t="s">
-        <v>478</v>
+      <c r="L99" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N99" s="10"/>
       <c r="T99" s="10"/>
-      <c r="W99" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X99" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y99" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z99" s="11" t="s">
-        <v>120</v>
+      <c r="W99" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X99" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y99" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z99" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB99" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD99" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>99</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K100" s="7"/>
-      <c r="L100" s="7" t="s">
-        <v>478</v>
+      <c r="L100" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N100" s="10"/>
       <c r="T100" s="10"/>
-      <c r="W100" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X100" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y100" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z100" s="11" t="s">
-        <v>120</v>
+      <c r="W100" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X100" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y100" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z100" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB100" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD100" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="9">
         <v>100</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K101" s="7"/>
-      <c r="L101" s="7" t="s">
-        <v>478</v>
+      <c r="L101" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="T101" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="W101" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X101" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y101" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z101" s="11" t="s">
-        <v>120</v>
+        <v>560</v>
+      </c>
+      <c r="W101" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X101" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y101" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z101" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AA101" s="10" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="AB101" s="14" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+      <c r="AD101" s="9" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="9">
         <v>101</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K102" s="7"/>
-      <c r="L102" s="7" t="s">
-        <v>478</v>
+      <c r="L102" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N102" s="10"/>
       <c r="T102" s="10"/>
-      <c r="W102" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X102" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y102" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z102" s="11" t="s">
-        <v>120</v>
+      <c r="W102" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X102" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y102" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z102" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB102" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD102" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>102</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K103" s="7"/>
-      <c r="L103" s="7" t="s">
-        <v>478</v>
+      <c r="L103" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N103" s="10"/>
       <c r="T103" s="10"/>
-      <c r="W103" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X103" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y103" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z103" s="11" t="s">
-        <v>120</v>
+      <c r="W103" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X103" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y103" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z103" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB103" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD103" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>103</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K104" s="7"/>
-      <c r="L104" s="7" t="s">
-        <v>478</v>
+      <c r="L104" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N104" s="10"/>
       <c r="T104" s="10"/>
-      <c r="W104" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X104" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y104" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z104" s="11" t="s">
-        <v>120</v>
+      <c r="W104" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X104" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y104" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z104" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB104" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD104" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="9">
         <v>104</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K105" s="7"/>
-      <c r="L105" s="7" t="s">
-        <v>478</v>
+      <c r="L105" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N105" s="10"/>
       <c r="T105" s="10"/>
-      <c r="W105" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X105" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y105" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z105" s="11" t="s">
-        <v>120</v>
+      <c r="W105" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X105" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y105" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z105" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB105" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD105" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>105</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K106" s="7"/>
-      <c r="L106" s="7" t="s">
-        <v>478</v>
+      <c r="L106" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N106" s="10"/>
       <c r="T106" s="10"/>
-      <c r="W106" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X106" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y106" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z106" s="11" t="s">
-        <v>120</v>
+      <c r="W106" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X106" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y106" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z106" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB106" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD106" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>106</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K107" s="7"/>
-      <c r="L107" s="7" t="s">
-        <v>478</v>
+      <c r="L107" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N107" s="10"/>
       <c r="T107" s="10"/>
-      <c r="W107" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X107" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y107" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z107" s="11" t="s">
-        <v>120</v>
+      <c r="W107" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X107" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y107" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z107" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB107" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD107" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>107</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K108" s="7"/>
-      <c r="L108" s="7" t="s">
-        <v>478</v>
+      <c r="L108" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N108" s="10"/>
       <c r="T108" s="10"/>
-      <c r="W108" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X108" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y108" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z108" s="11" t="s">
-        <v>120</v>
+      <c r="W108" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X108" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y108" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z108" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB108" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD108" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>108</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="K109" s="7"/>
-      <c r="L109" s="7" t="s">
-        <v>478</v>
+      <c r="L109" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N109" s="10"/>
       <c r="T109" s="10"/>
-      <c r="W109" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="X109" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y109" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z109" s="11" t="s">
-        <v>120</v>
+      <c r="W109" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="X109" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y109" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z109" s="14" t="s">
+        <v>173</v>
       </c>
       <c r="AB109" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+      <c r="AD109" s="10" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>109</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="K110" s="7"/>
-      <c r="L110" s="7" t="s">
-        <v>478</v>
+      <c r="L110" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N110" s="10"/>
       <c r="T110" s="10"/>
       <c r="W110" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X110" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y110" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z110" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="111" spans="1:29" ht="75" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30" ht="75" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>110</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="K111" s="7"/>
-      <c r="L111" s="7" t="s">
-        <v>478</v>
+      <c r="L111" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M111" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="T111" s="10"/>
       <c r="W111" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="X111" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="X111" s="14" t="s">
-        <v>121</v>
-      </c>
       <c r="Y111" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z111" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA111" s="10" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="AC111" s="14" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>111</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="K112" s="7"/>
-      <c r="L112" s="7" t="s">
-        <v>478</v>
+      <c r="L112" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N112" s="10"/>
       <c r="T112" s="10"/>
       <c r="W112" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X112" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y112" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z112" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>112</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K113" s="7"/>
-      <c r="L113" s="7" t="s">
-        <v>478</v>
+      <c r="L113" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="T113" s="10" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="W113" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X113" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X113" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y113" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z113" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="114" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>113</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K114" s="7"/>
-      <c r="L114" s="7" t="s">
-        <v>478</v>
+      <c r="L114" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="T114" s="10" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="W114" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X114" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X114" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y114" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z114" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="115" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>114</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="K115" s="7"/>
-      <c r="L115" s="7" t="s">
-        <v>478</v>
+      <c r="L115" s="8" t="s">
+        <v>477</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="T115" s="10" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="W115" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X115" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="X115" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Y115" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Z115" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.25">
@@ -9047,44 +9182,44 @@
         <v>115</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
+      <c r="L116" s="8"/>
       <c r="M116" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N116" s="10"/>
       <c r="T116" s="10"/>
       <c r="W116" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X116" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y116" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z116" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.25">
@@ -9092,44 +9227,44 @@
         <v>116</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K117" s="7"/>
-      <c r="L117" s="7"/>
+      <c r="L117" s="8"/>
       <c r="M117" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N117" s="10"/>
       <c r="T117" s="10"/>
       <c r="W117" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X117" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y117" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z117" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.25">
@@ -9137,44 +9272,44 @@
         <v>117</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
+      <c r="L118" s="8"/>
       <c r="M118" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N118" s="10"/>
       <c r="T118" s="10"/>
       <c r="W118" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X118" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y118" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z118" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.25">
@@ -9182,44 +9317,44 @@
         <v>118</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
+      <c r="L119" s="8"/>
       <c r="M119" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N119" s="10"/>
       <c r="T119" s="10"/>
       <c r="W119" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X119" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y119" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z119" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="120" spans="1:27" ht="375" x14ac:dyDescent="0.25">
@@ -9227,51 +9362,51 @@
         <v>119</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="K120" s="7"/>
+      <c r="L120" s="8"/>
+      <c r="M120" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="N120" s="10" t="s">
+        <v>665</v>
+      </c>
+      <c r="T120" s="10" t="s">
         <v>666</v>
       </c>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="10" t="s">
+      <c r="W120" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="X120" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y120" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="Z120" s="12" t="s">
         <v>667</v>
       </c>
-      <c r="N120" s="10" t="s">
+      <c r="AA120" s="10" t="s">
         <v>668</v>
-      </c>
-      <c r="T120" s="10" t="s">
-        <v>669</v>
-      </c>
-      <c r="W120" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="X120" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y120" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="Z120" s="12" t="s">
-        <v>670</v>
-      </c>
-      <c r="AA120" s="10" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.25">
@@ -9279,44 +9414,44 @@
         <v>120</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K121" s="7"/>
-      <c r="L121" s="7"/>
+      <c r="L121" s="8"/>
       <c r="M121" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N121" s="10"/>
       <c r="T121" s="10"/>
       <c r="W121" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X121" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y121" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z121" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.25">
@@ -9324,44 +9459,44 @@
         <v>121</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="K122" s="7"/>
-      <c r="L122" s="7"/>
+      <c r="L122" s="8"/>
       <c r="M122" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N122" s="10"/>
       <c r="T122" s="10"/>
       <c r="W122" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="X122" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Y122" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Z122" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-MSN.xlsx
+++ b/baseline/data_processing_elements-MSN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E0253F-D8C7-41E9-8CA3-CB21A7DDB1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCEA346-1EEF-40B3-99E1-A8B2B94BB00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSN" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>Must be unique within the study.</t>
-  </si>
-  <si>
-    <t>Deelnemer_ID</t>
   </si>
   <si>
     <t>particiapant ID</t>
@@ -2584,6 +2581,9 @@
   <si>
     <t>Available, but need to request and probably to clean. 
 To request and evaluate, but might not be compatible.</t>
+  </si>
+  <si>
+    <t>randomID</t>
   </si>
 </sst>
 </file>
@@ -3176,7 +3176,7 @@
         <v>28</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>29</v>
@@ -3216,23 +3216,23 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
       <c r="M2" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="N2" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>39</v>
       </c>
       <c r="T2" s="10"/>
       <c r="W2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="Y2" s="10" t="s">
-        <v>42</v>
-      </c>
       <c r="Z2" s="11" t="s">
-        <v>38</v>
+        <v>745</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -3243,13 +3243,13 @@
         <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>36</v>
@@ -3258,26 +3258,26 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="8"/>
       <c r="M3" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N3" s="10"/>
       <c r="T3" s="10"/>
       <c r="W3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -3288,13 +3288,13 @@
         <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>52</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>36</v>
@@ -3303,26 +3303,26 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8"/>
       <c r="M4" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N4" s="10"/>
       <c r="T4" s="10"/>
       <c r="W4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X4" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z4" s="12" t="s">
         <v>48</v>
-      </c>
-      <c r="Z4" s="12" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -3333,38 +3333,38 @@
         <v>32</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>56</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>57</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8"/>
       <c r="M5" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N5" s="10"/>
       <c r="T5" s="10"/>
       <c r="W5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X5" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y5" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z5" s="11">
         <v>1</v>
@@ -3378,50 +3378,50 @@
         <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="N6" s="10" t="s">
         <v>66</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>67</v>
       </c>
       <c r="T6" s="10"/>
       <c r="W6" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y6" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="Z6" s="11" t="s">
+      <c r="AA6" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="30" x14ac:dyDescent="0.25">
@@ -3432,16 +3432,16 @@
         <v>32</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>74</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -3449,28 +3449,28 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="N7" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="T7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="T7" s="10" t="s">
+      <c r="W7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="W7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Z7" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="Z7" s="11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -3481,47 +3481,47 @@
         <v>32</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>83</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="T8" s="10"/>
       <c r="W8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X8" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y8" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3532,49 +3532,49 @@
         <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="N9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="W9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y9" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="W9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X9" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Z9" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="Z9" s="11" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3585,52 +3585,52 @@
         <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>102</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>93</v>
-      </c>
       <c r="L10" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="T10" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="T10" s="10" t="s">
-        <v>97</v>
-      </c>
       <c r="W10" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3641,51 +3641,51 @@
         <v>32</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>106</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="M11" s="10" t="s">
+      <c r="N11" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="T11" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="T11" s="10" t="s">
+      <c r="W11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z11" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="W11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z11" s="11" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3696,50 +3696,50 @@
         <v>32</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>118</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N12" s="10"/>
       <c r="T12" s="10"/>
       <c r="V12" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="W12" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X12" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X12" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y12" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3750,50 +3750,50 @@
         <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N13" s="10"/>
       <c r="T13" s="10"/>
       <c r="V13" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="W13" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X13" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X13" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y13" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3804,50 +3804,50 @@
         <v>32</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>128</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>130</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N14" s="10"/>
       <c r="T14" s="10"/>
       <c r="V14" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="W14" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X14" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X14" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y14" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3858,50 +3858,50 @@
         <v>32</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>133</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>135</v>
-      </c>
       <c r="K15" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N15" s="10"/>
       <c r="T15" s="10"/>
       <c r="V15" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="W15" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X15" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X15" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y15" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3912,50 +3912,50 @@
         <v>32</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>138</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="K16" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N16" s="10"/>
       <c r="T16" s="10"/>
       <c r="V16" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="W16" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X16" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X16" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y16" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -3966,50 +3966,50 @@
         <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>143</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="K17" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N17" s="10"/>
       <c r="T17" s="10"/>
       <c r="V17" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="W17" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X17" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X17" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y17" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -4020,50 +4020,50 @@
         <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>150</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N18" s="10"/>
       <c r="T18" s="10"/>
       <c r="V18" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W18" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X18" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X18" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y18" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4074,50 +4074,50 @@
         <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>153</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>156</v>
-      </c>
       <c r="L19" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N19" s="10"/>
       <c r="T19" s="10"/>
       <c r="V19" s="10" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="W19" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X19" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="X19" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="Y19" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z19" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="150" x14ac:dyDescent="0.25">
@@ -4128,59 +4128,59 @@
         <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>159</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="N20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="T20" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="T20" s="10" t="s">
+      <c r="V20" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="W20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X20" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z20" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="W20" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X20" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y20" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z20" s="11" t="s">
-        <v>166</v>
-      </c>
       <c r="AB20" s="14" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AD20" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -4191,62 +4191,62 @@
         <v>32</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>169</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="L21" s="8" t="s">
-        <v>172</v>
-      </c>
       <c r="M21" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="P21" s="14" t="s">
         <v>673</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>675</v>
-      </c>
-      <c r="P21" s="14" t="s">
-        <v>674</v>
       </c>
       <c r="T21" s="10"/>
       <c r="W21" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z21" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA21" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="X21" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y21" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z21" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA21" s="10" t="s">
-        <v>174</v>
-      </c>
       <c r="AB21" s="14" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AD21" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4257,19 +4257,19 @@
         <v>32</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4277,21 +4277,21 @@
       <c r="K22" s="7"/>
       <c r="L22" s="8"/>
       <c r="M22" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N22" s="10"/>
       <c r="T22" s="10"/>
       <c r="W22" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="120" x14ac:dyDescent="0.25">
@@ -4302,13 +4302,13 @@
         <v>32</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>36</v>
@@ -4320,43 +4320,43 @@
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23" s="14" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N23" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="P23" s="10" t="s">
         <v>679</v>
       </c>
-      <c r="P23" s="10" t="s">
-        <v>680</v>
-      </c>
       <c r="T23" s="10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="V23" s="14" t="s">
+        <v>689</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y23" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z23" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA23" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB23" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="AC23" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="W23" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X23" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y23" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z23" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA23" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB23" s="14" t="s">
-        <v>692</v>
-      </c>
-      <c r="AC23" s="10" t="s">
-        <v>691</v>
-      </c>
       <c r="AD23" s="10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="150" x14ac:dyDescent="0.25">
@@ -4367,47 +4367,47 @@
         <v>32</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="T24" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="W24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z24" s="11" t="s">
         <v>188</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="T24" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="W24" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z24" s="11" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -4418,16 +4418,16 @@
         <v>32</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>192</v>
-      </c>
       <c r="F25" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -4435,31 +4435,31 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="N25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="T25" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="V25" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="V25" s="10" t="s">
-        <v>197</v>
-      </c>
       <c r="W25" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X25" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z25" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -4470,57 +4470,57 @@
         <v>32</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>200</v>
-      </c>
       <c r="F26" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="L26" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="L26" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="M26" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N26" s="10"/>
       <c r="T26" s="10"/>
       <c r="W26" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X26" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y26" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z26" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA26" s="10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AB26" s="14" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AC26" s="10" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AD26" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4531,47 +4531,47 @@
         <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>207</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>208</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="N27" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="T27" s="10"/>
       <c r="W27" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X27" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X27" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y27" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z27" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4582,16 +4582,16 @@
         <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>214</v>
-      </c>
       <c r="E28" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -4599,24 +4599,24 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N28" s="10"/>
       <c r="T28" s="10"/>
       <c r="W28" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X28" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y28" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Y28" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="Z28" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4627,47 +4627,47 @@
         <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>219</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>220</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="T29" s="10"/>
       <c r="W29" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X29" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y29" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z29" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4678,16 +4678,16 @@
         <v>32</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>223</v>
-      </c>
       <c r="E30" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -4695,24 +4695,24 @@
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N30" s="10"/>
       <c r="T30" s="10"/>
       <c r="W30" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y30" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Y30" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="Z30" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -4723,47 +4723,47 @@
         <v>32</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>228</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="L31" s="8"/>
       <c r="M31" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="N31" s="10" t="s">
         <v>229</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>230</v>
       </c>
       <c r="T31" s="10"/>
       <c r="W31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X31" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X31" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y31" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z31" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -4774,50 +4774,50 @@
         <v>32</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>233</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>209</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>210</v>
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="N32" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="T32" s="10"/>
       <c r="V32" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="W32" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X32" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z32" s="11" t="s">
         <v>236</v>
-      </c>
-      <c r="W32" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X32" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z32" s="11" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -4828,16 +4828,16 @@
         <v>32</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>239</v>
-      </c>
       <c r="E33" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -4845,24 +4845,24 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N33" s="10"/>
       <c r="T33" s="10"/>
       <c r="W33" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X33" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y33" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Y33" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="Z33" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
@@ -4873,19 +4873,19 @@
         <v>32</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="F34" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>243</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>244</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -4893,23 +4893,23 @@
       <c r="K34" s="7"/>
       <c r="L34" s="8"/>
       <c r="M34" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="N34" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="T34" s="10"/>
       <c r="W34" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X34" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X34" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y34" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z34" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -4920,16 +4920,16 @@
         <v>32</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>248</v>
-      </c>
       <c r="E35" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -4938,23 +4938,23 @@
       <c r="K35" s="7"/>
       <c r="L35" s="8"/>
       <c r="M35" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="N35" s="10" t="s">
         <v>245</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>246</v>
       </c>
       <c r="T35" s="10"/>
       <c r="W35" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X35" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y35" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="Y35" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="Z35" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -4965,52 +4965,52 @@
         <v>32</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>253</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K36" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="N36" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="T36" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="V36" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="V36" s="9" t="s">
+      <c r="W36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X36" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z36" s="11" t="s">
         <v>259</v>
-      </c>
-      <c r="W36" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X36" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y36" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z36" s="11" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
@@ -5021,50 +5021,50 @@
         <v>32</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>263</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>255</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="N37" s="10" t="s">
         <v>264</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>265</v>
       </c>
       <c r="T37" s="10"/>
       <c r="V37" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="W37" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X37" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y37" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z37" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -5075,50 +5075,50 @@
         <v>32</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>269</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>270</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="N38" s="10" t="s">
         <v>272</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="T38" s="10"/>
       <c r="V38" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="W38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X38" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z38" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="W38" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X38" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z38" s="11" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -5129,50 +5129,50 @@
         <v>32</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>277</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>279</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>280</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="N39" s="10" t="s">
         <v>281</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="T39" s="10"/>
       <c r="V39" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="W39" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z39" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="W39" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X39" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y39" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z39" s="11" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5183,16 +5183,16 @@
         <v>32</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="E40" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>287</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -5200,21 +5200,21 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N40" s="10"/>
       <c r="T40" s="10"/>
       <c r="W40" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X40" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X40" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y40" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z40" s="11">
         <v>2</v>
@@ -5228,19 +5228,19 @@
         <v>32</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="E41" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>290</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>291</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -5248,27 +5248,27 @@
       <c r="K41" s="7"/>
       <c r="L41" s="8"/>
       <c r="M41" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N41" s="10"/>
       <c r="T41" s="10"/>
       <c r="W41" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X41" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC41" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
@@ -5279,19 +5279,19 @@
         <v>32</v>
       </c>
       <c r="C42" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="E42" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>294</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>295</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -5299,23 +5299,23 @@
       <c r="K42" s="7"/>
       <c r="L42" s="8"/>
       <c r="M42" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="N42" s="10" t="s">
         <v>296</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>297</v>
       </c>
       <c r="T42" s="10"/>
       <c r="W42" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X42" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X42" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y42" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
@@ -5326,19 +5326,19 @@
         <v>32</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="E43" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>300</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
@@ -5346,23 +5346,23 @@
       <c r="K43" s="7"/>
       <c r="L43" s="8"/>
       <c r="M43" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="N43" s="10" t="s">
         <v>301</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>302</v>
       </c>
       <c r="T43" s="10"/>
       <c r="W43" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X43" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X43" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y43" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z43" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
@@ -5373,19 +5373,19 @@
         <v>32</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>304</v>
-      </c>
       <c r="E44" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -5393,23 +5393,23 @@
       <c r="K44" s="7"/>
       <c r="L44" s="8"/>
       <c r="M44" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="N44" s="10" t="s">
         <v>305</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>306</v>
       </c>
       <c r="T44" s="10"/>
       <c r="W44" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X44" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X44" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y44" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z44" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
@@ -5420,19 +5420,19 @@
         <v>32</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>308</v>
-      </c>
       <c r="E45" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -5440,23 +5440,23 @@
       <c r="K45" s="7"/>
       <c r="L45" s="8"/>
       <c r="M45" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="N45" s="10" t="s">
         <v>309</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>310</v>
       </c>
       <c r="T45" s="10"/>
       <c r="W45" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X45" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X45" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y45" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z45" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -5467,48 +5467,48 @@
         <v>32</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="E46" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
       <c r="J46" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="8"/>
       <c r="M46" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="N46" s="10" t="s">
         <v>314</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="T46" s="10"/>
       <c r="V46" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="W46" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X46" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y46" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z46" s="11" t="s">
         <v>316</v>
-      </c>
-      <c r="W46" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X46" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y46" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z46" s="11" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
@@ -5519,19 +5519,19 @@
         <v>32</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>319</v>
-      </c>
       <c r="E47" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -5539,23 +5539,23 @@
       <c r="K47" s="7"/>
       <c r="L47" s="8"/>
       <c r="M47" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="N47" s="10" t="s">
         <v>320</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>321</v>
       </c>
       <c r="T47" s="10"/>
       <c r="W47" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X47" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X47" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y47" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z47" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5566,19 +5566,19 @@
         <v>32</v>
       </c>
       <c r="C48" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>323</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>324</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -5586,28 +5586,28 @@
       <c r="K48" s="7"/>
       <c r="L48" s="8"/>
       <c r="M48" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="N48" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="N48" s="10" t="s">
+      <c r="T48" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="T48" s="10" t="s">
+      <c r="W48" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X48" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y48" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z48" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="W48" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X48" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y48" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z48" s="12" t="s">
+      <c r="AA48" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="AA48" s="10" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5618,49 +5618,49 @@
         <v>32</v>
       </c>
       <c r="C49" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>331</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>332</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="K49" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="N49" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="N49" s="10" t="s">
+      <c r="T49" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="T49" s="10" t="s">
+      <c r="W49" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X49" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y49" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z49" s="11" t="s">
         <v>337</v>
-      </c>
-      <c r="W49" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X49" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y49" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z49" s="11" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -5671,49 +5671,49 @@
         <v>32</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>340</v>
-      </c>
       <c r="E50" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="L50" s="8" t="s">
-        <v>342</v>
-      </c>
       <c r="M50" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N50" s="10"/>
       <c r="T50" s="10"/>
       <c r="W50" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X50" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y50" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z50" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA50" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AC50" s="10" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5724,52 +5724,52 @@
         <v>32</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>345</v>
-      </c>
       <c r="E51" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>346</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>347</v>
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="N51" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="N51" s="10" t="s">
+      <c r="T51" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="W51" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X51" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y51" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z51" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="T51" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="W51" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X51" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y51" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z51" s="12" t="s">
+      <c r="AA51" s="10" t="s">
         <v>350</v>
-      </c>
-      <c r="AA51" s="10" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5780,45 +5780,45 @@
         <v>32</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>353</v>
-      </c>
       <c r="E52" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="K52" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="K52" s="7" t="s">
-        <v>355</v>
-      </c>
       <c r="L52" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N52" s="10"/>
       <c r="T52" s="10"/>
       <c r="W52" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X52" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y52" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z52" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5829,19 +5829,19 @@
         <v>32</v>
       </c>
       <c r="C53" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -5849,28 +5849,28 @@
       <c r="K53" s="7"/>
       <c r="L53" s="8"/>
       <c r="M53" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="N53" s="10" t="s">
+      <c r="T53" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="W53" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X53" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y53" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z53" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="T53" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="W53" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X53" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y53" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z53" s="12" t="s">
-        <v>361</v>
-      </c>
       <c r="AA53" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="54" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5881,55 +5881,55 @@
         <v>32</v>
       </c>
       <c r="C54" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="E54" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>366</v>
       </c>
       <c r="L54" s="8"/>
       <c r="M54" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="N54" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="N54" s="10" t="s">
-        <v>368</v>
-      </c>
       <c r="T54" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="W54" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="X54" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Y54" s="10" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Z54" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AA54" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AC54" s="10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -5940,16 +5940,16 @@
         <v>32</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>370</v>
-      </c>
       <c r="E55" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -5957,37 +5957,37 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="M55" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="N55" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="T55" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="V55" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="W55" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X55" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y55" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z55" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA55" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="T55" s="10" t="s">
+      <c r="AC55" s="10" t="s">
         <v>697</v>
-      </c>
-      <c r="V55" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="W55" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="X55" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y55" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z55" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="AC55" s="10" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -5998,55 +5998,55 @@
         <v>32</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>375</v>
-      </c>
       <c r="E56" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="K56" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="L56" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="M56" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="N56" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="N56" s="10" t="s">
+      <c r="T56" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="T56" s="10" t="s">
+      <c r="W56" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X56" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y56" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z56" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="W56" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X56" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y56" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z56" s="11" t="s">
-        <v>382</v>
-      </c>
       <c r="AB56" s="14" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AD56" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -6057,54 +6057,54 @@
         <v>32</v>
       </c>
       <c r="C57" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>384</v>
-      </c>
       <c r="E57" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="M57" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="N57" s="10" t="s">
         <v>701</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>702</v>
       </c>
       <c r="T57" s="10"/>
       <c r="V57" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="W57" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="X57" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y57" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z57" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA57" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="AC57" s="10" t="s">
         <v>718</v>
-      </c>
-      <c r="W57" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="X57" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y57" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z57" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA57" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="AC57" s="10" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6115,54 +6115,54 @@
         <v>32</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="E58" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>388</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>389</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L58" s="8"/>
       <c r="M58" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N58" s="10"/>
       <c r="T58" s="10"/>
       <c r="W58" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X58" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y58" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z58" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB58" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AC58" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AD58" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
@@ -6173,19 +6173,19 @@
         <v>32</v>
       </c>
       <c r="C59" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>392</v>
-      </c>
       <c r="E59" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F59" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G59" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
@@ -6193,21 +6193,21 @@
       <c r="K59" s="7"/>
       <c r="L59" s="8"/>
       <c r="M59" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N59" s="10"/>
       <c r="T59" s="10"/>
       <c r="W59" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X59" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y59" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z59" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="135" x14ac:dyDescent="0.25">
@@ -6218,43 +6218,43 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>394</v>
-      </c>
       <c r="E60" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N60" s="10"/>
       <c r="T60" s="10"/>
       <c r="W60" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X60" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z60" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -6265,43 +6265,43 @@
         <v>32</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="E61" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>399</v>
-      </c>
       <c r="F61" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="L61" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="L61" s="8" t="s">
-        <v>401</v>
-      </c>
       <c r="M61" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N61" s="10"/>
       <c r="T61" s="10"/>
       <c r="W61" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X61" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y61" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z61" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6312,43 +6312,43 @@
         <v>32</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>403</v>
-      </c>
       <c r="E62" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N62" s="10"/>
       <c r="T62" s="10"/>
       <c r="W62" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X62" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y62" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z62" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6359,16 +6359,16 @@
         <v>32</v>
       </c>
       <c r="C63" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>407</v>
-      </c>
       <c r="E63" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -6376,24 +6376,24 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N63" s="10"/>
       <c r="T63" s="10"/>
       <c r="W63" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X63" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z63" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6404,16 +6404,16 @@
         <v>32</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>409</v>
-      </c>
       <c r="E64" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -6421,24 +6421,24 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N64" s="10"/>
       <c r="T64" s="10"/>
       <c r="W64" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X64" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y64" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z64" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:30" ht="165" x14ac:dyDescent="0.25">
@@ -6449,16 +6449,16 @@
         <v>32</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>412</v>
-      </c>
       <c r="F65" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -6466,24 +6466,24 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="8" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N65" s="10"/>
       <c r="T65" s="10"/>
       <c r="W65" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X65" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y65" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z65" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6494,43 +6494,43 @@
         <v>32</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="E66" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>416</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N66" s="10"/>
       <c r="T66" s="10"/>
       <c r="W66" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X66" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y66" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z66" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6541,43 +6541,43 @@
         <v>32</v>
       </c>
       <c r="C67" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="E67" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>419</v>
-      </c>
       <c r="F67" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N67" s="10"/>
       <c r="T67" s="10"/>
       <c r="W67" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X67" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z67" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
@@ -6588,43 +6588,43 @@
         <v>32</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>421</v>
-      </c>
       <c r="E68" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F68" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="G68" s="7" t="s">
         <v>177</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>178</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="8"/>
       <c r="M68" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N68" s="10"/>
       <c r="T68" s="10"/>
       <c r="W68" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X68" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y68" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z68" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -6635,16 +6635,16 @@
         <v>32</v>
       </c>
       <c r="C69" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="E69" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>424</v>
-      </c>
       <c r="F69" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -6652,24 +6652,24 @@
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N69" s="10"/>
       <c r="T69" s="10"/>
       <c r="W69" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X69" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y69" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z69" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -6680,61 +6680,61 @@
         <v>32</v>
       </c>
       <c r="C70" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="E70" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>428</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="L70" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="M70" s="14" t="s">
         <v>430</v>
       </c>
-      <c r="M70" s="14" t="s">
-        <v>431</v>
-      </c>
       <c r="N70" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="S70" s="16"/>
       <c r="T70" s="14"/>
       <c r="W70" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X70" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y70" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z70" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA70" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AB70" s="14" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AC70" s="10" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AD70" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="71" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -6745,43 +6745,43 @@
         <v>32</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D71" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="E71" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="E71" s="7" t="s">
-        <v>435</v>
-      </c>
       <c r="F71" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N71" s="10"/>
       <c r="T71" s="10"/>
       <c r="W71" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X71" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y71" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z71" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:30" ht="180" x14ac:dyDescent="0.25">
@@ -6792,65 +6792,65 @@
         <v>32</v>
       </c>
       <c r="C72" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="E72" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>439</v>
-      </c>
       <c r="F72" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M72" s="14" t="s">
+        <v>708</v>
+      </c>
+      <c r="N72" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="N72" s="10" t="s">
+      <c r="P72" s="10" t="s">
         <v>710</v>
       </c>
-      <c r="P72" s="10" t="s">
-        <v>711</v>
-      </c>
       <c r="T72" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="V72" s="14"/>
       <c r="W72" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X72" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y72" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z72" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA72" s="10" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AB72" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AC72" s="10" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AD72" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="73" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -6861,43 +6861,43 @@
         <v>32</v>
       </c>
       <c r="C73" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="E73" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="E73" s="7" t="s">
-        <v>444</v>
-      </c>
       <c r="F73" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N73" s="10"/>
       <c r="T73" s="10"/>
       <c r="W73" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X73" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y73" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z73" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -6908,49 +6908,49 @@
         <v>32</v>
       </c>
       <c r="C74" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="E74" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>448</v>
-      </c>
       <c r="F74" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M74" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="K74" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="M74" s="10" t="s">
+      <c r="N74" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="N74" s="10" t="s">
+      <c r="T74" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="W74" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X74" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y74" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z74" s="11" t="s">
         <v>451</v>
-      </c>
-      <c r="T74" s="10" t="s">
-        <v>327</v>
-      </c>
-      <c r="W74" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X74" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y74" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z74" s="11" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="75" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
@@ -6961,48 +6961,48 @@
         <v>32</v>
       </c>
       <c r="C75" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="E75" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>455</v>
-      </c>
       <c r="F75" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="8"/>
       <c r="M75" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="N75" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="N75" s="10" t="s">
+      <c r="T75" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="T75" s="10" t="s">
+      <c r="W75" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X75" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y75" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="W75" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X75" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y75" s="10" t="s">
-        <v>460</v>
-      </c>
       <c r="Z75" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="AC75" s="10" t="s">
         <v>725</v>
-      </c>
-      <c r="AC75" s="10" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="76" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
@@ -7013,19 +7013,19 @@
         <v>32</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="E76" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="F76" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>463</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>464</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
@@ -7033,26 +7033,26 @@
       <c r="K76" s="7"/>
       <c r="L76" s="8"/>
       <c r="M76" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N76" s="10"/>
       <c r="T76" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="W76" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X76" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y76" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="W76" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X76" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y76" s="10" t="s">
-        <v>460</v>
-      </c>
       <c r="Z76" s="11" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AC76" s="10" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="77" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -7063,47 +7063,47 @@
         <v>32</v>
       </c>
       <c r="C77" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>466</v>
-      </c>
       <c r="E77" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="L77" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="L77" s="8" t="s">
+      <c r="M77" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="N77" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="T77" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="N77" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="T77" s="10" t="s">
+      <c r="W77" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X77" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y77" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z77" s="11" t="s">
         <v>470</v>
-      </c>
-      <c r="W77" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X77" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y77" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z77" s="11" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="78" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7114,55 +7114,55 @@
         <v>32</v>
       </c>
       <c r="C78" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="E78" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="F78" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="K78" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="K78" s="7" t="s">
+      <c r="L78" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="L78" s="8" t="s">
+      <c r="M78" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="M78" s="10" t="s">
+      <c r="N78" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="T78" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="W78" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X78" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y78" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z78" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="N78" s="10" t="s">
-        <v>740</v>
-      </c>
-      <c r="T78" s="10" t="s">
+      <c r="AA78" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="AD78" s="9" t="s">
         <v>741</v>
-      </c>
-      <c r="W78" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X78" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y78" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z78" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="AA78" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="AD78" s="9" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="79" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7173,54 +7173,54 @@
         <v>32</v>
       </c>
       <c r="C79" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="E79" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>483</v>
-      </c>
       <c r="F79" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>485</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N79" s="10"/>
       <c r="T79" s="10"/>
       <c r="W79" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X79" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y79" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z79" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA79" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AB79" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD79" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="80" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7231,58 +7231,58 @@
         <v>32</v>
       </c>
       <c r="C80" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="E80" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="E80" s="7" t="s">
-        <v>489</v>
-      </c>
       <c r="F80" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N80" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="T80" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="T80" s="10" t="s">
+      <c r="W80" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X80" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y80" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z80" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA80" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="W80" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X80" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y80" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z80" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA80" s="10" t="s">
-        <v>493</v>
-      </c>
       <c r="AB80" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD80" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="81" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7293,58 +7293,58 @@
         <v>32</v>
       </c>
       <c r="C81" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="E81" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>496</v>
-      </c>
       <c r="F81" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N81" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="T81" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="T81" s="10" t="s">
+      <c r="W81" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X81" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y81" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z81" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA81" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="W81" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X81" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y81" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z81" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA81" s="10" t="s">
-        <v>500</v>
-      </c>
       <c r="AB81" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD81" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="82" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7355,58 +7355,58 @@
         <v>32</v>
       </c>
       <c r="C82" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="E82" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="E82" s="7" t="s">
-        <v>503</v>
-      </c>
       <c r="F82" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N82" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="T82" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="W82" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X82" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y82" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z82" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA82" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="T82" s="15" t="s">
-        <v>492</v>
-      </c>
-      <c r="W82" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X82" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y82" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z82" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA82" s="10" t="s">
-        <v>506</v>
-      </c>
       <c r="AB82" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD82" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="83" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7417,45 +7417,45 @@
         <v>32</v>
       </c>
       <c r="C83" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="E83" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>509</v>
-      </c>
       <c r="F83" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N83" s="10"/>
       <c r="T83" s="10"/>
       <c r="W83" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X83" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y83" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z83" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="84" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7466,49 +7466,49 @@
         <v>32</v>
       </c>
       <c r="C84" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="E84" s="7" t="s">
         <v>512</v>
       </c>
-      <c r="E84" s="7" t="s">
-        <v>513</v>
-      </c>
       <c r="F84" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M84" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="N84" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="N84" s="10" t="s">
+      <c r="T84" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="T84" s="10" t="s">
-        <v>517</v>
-      </c>
       <c r="W84" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X84" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X84" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y84" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z84" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="85" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7519,53 +7519,53 @@
         <v>32</v>
       </c>
       <c r="C85" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="E85" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>520</v>
-      </c>
       <c r="F85" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="K85" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="K85" s="7" t="s">
-        <v>523</v>
-      </c>
       <c r="L85" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N85" s="10"/>
       <c r="T85" s="10"/>
       <c r="W85" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X85" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y85" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z85" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB85" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AD85" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="86" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7576,58 +7576,58 @@
         <v>32</v>
       </c>
       <c r="C86" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="E86" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>526</v>
-      </c>
       <c r="F86" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N86" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="T86" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="T86" s="10" t="s">
+      <c r="W86" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X86" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y86" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z86" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA86" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="W86" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X86" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y86" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z86" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA86" s="10" t="s">
-        <v>530</v>
-      </c>
       <c r="AB86" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AD86" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="87" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -7638,50 +7638,50 @@
         <v>32</v>
       </c>
       <c r="C87" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="E87" s="7" t="s">
-        <v>533</v>
-      </c>
       <c r="F87" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M87" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="N87" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="T87" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="T87" s="10" t="s">
+      <c r="V87" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="V87" s="10" t="s">
+      <c r="W87" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X87" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y87" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z87" s="11" t="s">
         <v>538</v>
-      </c>
-      <c r="W87" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X87" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y87" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z87" s="11" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="88" spans="1:30" ht="105" x14ac:dyDescent="0.25">
@@ -7692,51 +7692,51 @@
         <v>32</v>
       </c>
       <c r="C88" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="E88" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="E88" s="7" t="s">
-        <v>542</v>
-      </c>
       <c r="F88" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="K88" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="J88" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="K88" s="7" t="s">
+      <c r="L88" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="M88" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="L88" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="M88" s="10" t="s">
+      <c r="N88" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="N88" s="10" t="s">
+      <c r="T88" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="T88" s="10" t="s">
+      <c r="W88" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X88" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y88" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z88" s="11" t="s">
         <v>547</v>
-      </c>
-      <c r="W88" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X88" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y88" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z88" s="11" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="89" spans="1:30" ht="105" x14ac:dyDescent="0.25">
@@ -7747,47 +7747,47 @@
         <v>32</v>
       </c>
       <c r="C89" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="D89" s="7" t="s">
-        <v>550</v>
-      </c>
       <c r="E89" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="L89" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="L89" s="8" t="s">
+      <c r="M89" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="T89" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="W89" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X89" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y89" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z89" s="11" t="s">
         <v>552</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="N89" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="T89" s="10" t="s">
-        <v>547</v>
-      </c>
-      <c r="W89" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X89" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y89" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z89" s="11" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="90" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7798,58 +7798,58 @@
         <v>32</v>
       </c>
       <c r="C90" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="E90" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>556</v>
-      </c>
       <c r="F90" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="K90" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="K90" s="7" t="s">
+      <c r="L90" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N90" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="L90" s="8" t="s">
-        <v>477</v>
-      </c>
-      <c r="M90" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N90" s="10" t="s">
+      <c r="T90" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="T90" s="10" t="s">
+      <c r="W90" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X90" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y90" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z90" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA90" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="W90" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X90" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y90" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z90" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA90" s="10" t="s">
-        <v>561</v>
-      </c>
       <c r="AB90" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AD90" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="91" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7860,55 +7860,55 @@
         <v>32</v>
       </c>
       <c r="C91" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="D91" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="E91" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="E91" s="7" t="s">
-        <v>564</v>
-      </c>
       <c r="F91" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N91" s="10"/>
       <c r="T91" s="10"/>
       <c r="W91" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X91" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y91" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z91" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AA91" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AB91" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AC91" s="10" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD91" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="92" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7919,49 +7919,49 @@
         <v>32</v>
       </c>
       <c r="C92" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="E92" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="E92" s="7" t="s">
-        <v>569</v>
-      </c>
       <c r="F92" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N92" s="10"/>
       <c r="T92" s="10"/>
       <c r="W92" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X92" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y92" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z92" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB92" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD92" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="93" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7972,49 +7972,49 @@
         <v>32</v>
       </c>
       <c r="C93" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D93" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="E93" s="7" t="s">
         <v>571</v>
       </c>
-      <c r="E93" s="7" t="s">
-        <v>572</v>
-      </c>
       <c r="F93" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N93" s="10"/>
       <c r="T93" s="10"/>
       <c r="W93" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X93" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y93" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z93" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB93" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD93" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="94" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8025,49 +8025,49 @@
         <v>32</v>
       </c>
       <c r="C94" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="D94" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="E94" s="7" t="s">
         <v>574</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>575</v>
-      </c>
       <c r="F94" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N94" s="10"/>
       <c r="T94" s="10"/>
       <c r="W94" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X94" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y94" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z94" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB94" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD94" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="95" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8078,49 +8078,49 @@
         <v>32</v>
       </c>
       <c r="C95" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="D95" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="E95" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="E95" s="7" t="s">
-        <v>578</v>
-      </c>
       <c r="F95" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N95" s="10"/>
       <c r="T95" s="10"/>
       <c r="W95" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X95" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y95" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z95" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB95" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD95" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="96" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8131,49 +8131,49 @@
         <v>32</v>
       </c>
       <c r="C96" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="E96" s="7" t="s">
         <v>580</v>
       </c>
-      <c r="E96" s="7" t="s">
-        <v>581</v>
-      </c>
       <c r="F96" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N96" s="10"/>
       <c r="T96" s="10"/>
       <c r="W96" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X96" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y96" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z96" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB96" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD96" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="97" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8184,49 +8184,49 @@
         <v>32</v>
       </c>
       <c r="C97" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="D97" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="E97" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>584</v>
-      </c>
       <c r="F97" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N97" s="10"/>
       <c r="T97" s="10"/>
       <c r="W97" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X97" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y97" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z97" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB97" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD97" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="98" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8237,49 +8237,49 @@
         <v>32</v>
       </c>
       <c r="C98" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="D98" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="E98" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>587</v>
-      </c>
       <c r="F98" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N98" s="10"/>
       <c r="T98" s="10"/>
       <c r="W98" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X98" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y98" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z98" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB98" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD98" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="99" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8290,49 +8290,49 @@
         <v>32</v>
       </c>
       <c r="C99" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="D99" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="E99" s="7" t="s">
         <v>589</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>590</v>
-      </c>
       <c r="F99" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N99" s="10"/>
       <c r="T99" s="10"/>
       <c r="W99" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X99" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y99" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z99" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB99" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD99" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="100" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8343,49 +8343,49 @@
         <v>32</v>
       </c>
       <c r="C100" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="E100" s="7" t="s">
         <v>592</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>593</v>
-      </c>
       <c r="F100" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N100" s="10"/>
       <c r="T100" s="10"/>
       <c r="W100" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X100" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y100" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z100" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB100" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD100" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="101" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8396,56 +8396,56 @@
         <v>32</v>
       </c>
       <c r="C101" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="D101" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="E101" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>596</v>
-      </c>
       <c r="F101" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N101" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="T101" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="W101" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="X101" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y101" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z101" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA101" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="T101" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="W101" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X101" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Y101" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z101" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA101" s="10" t="s">
-        <v>598</v>
-      </c>
       <c r="AB101" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AD101" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="102" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8456,49 +8456,49 @@
         <v>32</v>
       </c>
       <c r="C102" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="E102" s="7" t="s">
         <v>600</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>601</v>
-      </c>
       <c r="F102" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N102" s="10"/>
       <c r="T102" s="10"/>
       <c r="W102" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X102" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y102" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z102" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB102" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD102" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="103" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8509,49 +8509,49 @@
         <v>32</v>
       </c>
       <c r="C103" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="D103" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="E103" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>604</v>
-      </c>
       <c r="F103" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N103" s="10"/>
       <c r="T103" s="10"/>
       <c r="W103" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X103" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y103" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z103" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB103" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD103" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="104" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8562,49 +8562,49 @@
         <v>32</v>
       </c>
       <c r="C104" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="D104" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="E104" s="7" t="s">
         <v>606</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>607</v>
-      </c>
       <c r="F104" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N104" s="10"/>
       <c r="T104" s="10"/>
       <c r="W104" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X104" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y104" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z104" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB104" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD104" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="105" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8615,49 +8615,49 @@
         <v>32</v>
       </c>
       <c r="C105" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="E105" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>610</v>
-      </c>
       <c r="F105" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N105" s="10"/>
       <c r="T105" s="10"/>
       <c r="W105" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X105" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y105" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z105" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB105" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD105" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="106" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8668,49 +8668,49 @@
         <v>32</v>
       </c>
       <c r="C106" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="E106" s="7" t="s">
         <v>612</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>613</v>
-      </c>
       <c r="F106" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N106" s="10"/>
       <c r="T106" s="10"/>
       <c r="W106" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X106" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y106" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z106" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB106" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD106" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="107" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8721,49 +8721,49 @@
         <v>32</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="E107" s="7" t="s">
         <v>615</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>616</v>
-      </c>
       <c r="F107" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N107" s="10"/>
       <c r="T107" s="10"/>
       <c r="W107" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X107" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y107" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z107" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB107" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD107" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="108" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8774,49 +8774,49 @@
         <v>32</v>
       </c>
       <c r="C108" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="D108" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="E108" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>619</v>
-      </c>
       <c r="F108" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N108" s="10"/>
       <c r="T108" s="10"/>
       <c r="W108" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X108" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y108" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z108" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB108" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD108" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="109" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8827,49 +8827,49 @@
         <v>32</v>
       </c>
       <c r="C109" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D109" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="E109" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>622</v>
-      </c>
       <c r="F109" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N109" s="10"/>
       <c r="T109" s="10"/>
       <c r="W109" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X109" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Y109" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Z109" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB109" s="14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AD109" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="110" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8880,43 +8880,43 @@
         <v>32</v>
       </c>
       <c r="C110" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="D110" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="E110" s="7" t="s">
         <v>624</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>625</v>
-      </c>
       <c r="F110" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N110" s="10"/>
       <c r="T110" s="10"/>
       <c r="W110" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X110" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y110" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z110" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -8927,54 +8927,54 @@
         <v>32</v>
       </c>
       <c r="C111" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D111" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="E111" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="E111" s="7" t="s">
-        <v>629</v>
-      </c>
       <c r="F111" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M111" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N111" s="10" t="s">
+        <v>715</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>716</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>717</v>
       </c>
       <c r="T111" s="10"/>
       <c r="W111" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="X111" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="X111" s="14" t="s">
-        <v>120</v>
-      </c>
       <c r="Y111" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z111" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AA111" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AC111" s="14" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="112" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8985,43 +8985,43 @@
         <v>32</v>
       </c>
       <c r="C112" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="D112" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="E112" s="7" t="s">
         <v>633</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>634</v>
-      </c>
       <c r="F112" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N112" s="10"/>
       <c r="T112" s="10"/>
       <c r="W112" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X112" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y112" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z112" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9032,47 +9032,47 @@
         <v>32</v>
       </c>
       <c r="C113" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="D113" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>636</v>
-      </c>
       <c r="E113" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M113" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="N113" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="N113" s="10" t="s">
-        <v>639</v>
-      </c>
       <c r="T113" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="W113" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X113" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X113" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y113" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z113" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9083,47 +9083,47 @@
         <v>32</v>
       </c>
       <c r="C114" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="D114" s="7" t="s">
         <v>640</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>641</v>
-      </c>
       <c r="E114" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M114" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="N114" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="N114" s="10" t="s">
-        <v>644</v>
-      </c>
       <c r="T114" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="W114" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X114" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X114" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y114" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z114" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9134,47 +9134,47 @@
         <v>32</v>
       </c>
       <c r="C115" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="D115" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>646</v>
-      </c>
       <c r="E115" s="7" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M115" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="N115" s="10" t="s">
         <v>647</v>
       </c>
-      <c r="N115" s="10" t="s">
-        <v>648</v>
-      </c>
       <c r="T115" s="10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="W115" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X115" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="X115" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Y115" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Z115" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.25">
@@ -9185,41 +9185,41 @@
         <v>32</v>
       </c>
       <c r="C116" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>649</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>650</v>
-      </c>
       <c r="E116" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="8"/>
       <c r="M116" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N116" s="10"/>
       <c r="T116" s="10"/>
       <c r="W116" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X116" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y116" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z116" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.25">
@@ -9230,41 +9230,41 @@
         <v>32</v>
       </c>
       <c r="C117" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D117" s="7" t="s">
         <v>652</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>653</v>
-      </c>
       <c r="E117" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="8"/>
       <c r="M117" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N117" s="10"/>
       <c r="T117" s="10"/>
       <c r="W117" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X117" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y117" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z117" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.25">
@@ -9275,41 +9275,41 @@
         <v>32</v>
       </c>
       <c r="C118" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="D118" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>656</v>
-      </c>
       <c r="E118" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="8"/>
       <c r="M118" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N118" s="10"/>
       <c r="T118" s="10"/>
       <c r="W118" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X118" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y118" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z118" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.25">
@@ -9320,41 +9320,41 @@
         <v>32</v>
       </c>
       <c r="C119" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D119" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="D119" s="7" t="s">
-        <v>659</v>
-      </c>
       <c r="E119" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="8"/>
       <c r="M119" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N119" s="10"/>
       <c r="T119" s="10"/>
       <c r="W119" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X119" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y119" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z119" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:27" ht="375" x14ac:dyDescent="0.25">
@@ -9365,48 +9365,48 @@
         <v>32</v>
       </c>
       <c r="C120" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="D120" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>662</v>
-      </c>
       <c r="E120" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="8"/>
       <c r="M120" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="N120" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="N120" s="10" t="s">
+      <c r="T120" s="10" t="s">
         <v>665</v>
       </c>
-      <c r="T120" s="10" t="s">
+      <c r="W120" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="X120" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y120" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="Z120" s="12" t="s">
         <v>666</v>
       </c>
-      <c r="W120" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="X120" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Y120" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="Z120" s="12" t="s">
+      <c r="AA120" s="10" t="s">
         <v>667</v>
-      </c>
-      <c r="AA120" s="10" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.25">
@@ -9417,41 +9417,41 @@
         <v>32</v>
       </c>
       <c r="C121" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="D121" s="7" t="s">
         <v>669</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>670</v>
-      </c>
       <c r="E121" s="7" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="8"/>
       <c r="M121" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N121" s="10"/>
       <c r="T121" s="10"/>
       <c r="W121" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X121" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y121" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z121" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.25">
@@ -9462,41 +9462,41 @@
         <v>32</v>
       </c>
       <c r="C122" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="D122" s="7" t="s">
         <v>671</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>672</v>
-      </c>
       <c r="E122" s="7" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="8"/>
       <c r="M122" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N122" s="10"/>
       <c r="T122" s="10"/>
       <c r="W122" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="X122" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y122" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Z122" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-MSN.xlsx
+++ b/baseline/data_processing_elements-MSN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCEA346-1EEF-40B3-99E1-A8B2B94BB00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D814D6F9-E04B-4791-A9D9-2A5BBB89AA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>Must be unique within the study.</t>
-  </si>
-  <si>
-    <t>particiapant ID</t>
   </si>
   <si>
     <t>complete</t>
@@ -2583,7 +2580,10 @@
 To request and evaluate, but might not be compatible.</t>
   </si>
   <si>
-    <t>randomID</t>
+    <t>Deelnemer_ID</t>
+  </si>
+  <si>
+    <t>participant ID</t>
   </si>
 </sst>
 </file>
@@ -3176,7 +3176,7 @@
         <v>28</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>29</v>
@@ -3216,23 +3216,23 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
       <c r="M2" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="N2" s="10" t="s">
         <v>745</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>38</v>
       </c>
       <c r="T2" s="10"/>
       <c r="W2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X2" s="10" t="s">
+      <c r="Y2" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="Y2" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="Z2" s="11" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -3243,13 +3243,13 @@
         <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>36</v>
@@ -3258,26 +3258,26 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="8"/>
       <c r="M3" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N3" s="10"/>
       <c r="T3" s="10"/>
       <c r="W3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z3" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="Z3" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -3288,13 +3288,13 @@
         <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>51</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>36</v>
@@ -3303,26 +3303,26 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8"/>
       <c r="M4" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N4" s="10"/>
       <c r="T4" s="10"/>
       <c r="W4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X4" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z4" s="12" t="s">
         <v>47</v>
-      </c>
-      <c r="Z4" s="12" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
@@ -3333,38 +3333,38 @@
         <v>32</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8"/>
       <c r="M5" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N5" s="10"/>
       <c r="T5" s="10"/>
       <c r="W5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X5" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y5" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z5" s="11">
         <v>1</v>
@@ -3378,50 +3378,50 @@
         <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>64</v>
       </c>
       <c r="L6" s="8"/>
       <c r="M6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="T6" s="10"/>
       <c r="W6" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y6" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="Y6" s="10" t="s">
+      <c r="Z6" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="Z6" s="11" t="s">
+      <c r="AA6" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="30" x14ac:dyDescent="0.25">
@@ -3432,16 +3432,16 @@
         <v>32</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="F7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -3449,28 +3449,28 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M7" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="N7" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="T7" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="T7" s="10" t="s">
+      <c r="W7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y7" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="W7" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X7" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Z7" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="Z7" s="11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
@@ -3481,47 +3481,47 @@
         <v>32</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="F8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>84</v>
       </c>
       <c r="L8" s="8"/>
       <c r="M8" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="T8" s="10"/>
       <c r="W8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X8" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y8" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z8" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3532,49 +3532,49 @@
         <v>32</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>90</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
       <c r="J9" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="N9" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="T9" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="T9" s="10" t="s">
+      <c r="W9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y9" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="W9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X9" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y9" s="10" t="s">
+      <c r="Z9" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="Z9" s="11" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="165" x14ac:dyDescent="0.25">
@@ -3585,52 +3585,52 @@
         <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>101</v>
-      </c>
       <c r="F10" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>92</v>
-      </c>
       <c r="L10" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="N10" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="T10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="T10" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="W10" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X10" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3641,51 +3641,51 @@
         <v>32</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>105</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="K11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="L11" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="L11" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="M11" s="10" t="s">
+      <c r="N11" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="T11" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="T11" s="10" t="s">
+      <c r="W11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z11" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="W11" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X11" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z11" s="11" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3696,50 +3696,50 @@
         <v>32</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>115</v>
-      </c>
       <c r="F12" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="K12" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N12" s="10"/>
       <c r="T12" s="10"/>
       <c r="V12" s="10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="W12" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X12" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X12" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y12" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z12" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3750,50 +3750,50 @@
         <v>32</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>122</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>124</v>
-      </c>
       <c r="K13" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N13" s="10"/>
       <c r="T13" s="10"/>
       <c r="V13" s="10" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="W13" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X13" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X13" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y13" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z13" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3804,50 +3804,50 @@
         <v>32</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>127</v>
-      </c>
       <c r="F14" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="J14" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="K14" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N14" s="10"/>
       <c r="T14" s="10"/>
       <c r="V14" s="10" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="W14" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X14" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X14" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y14" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z14" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3858,50 +3858,50 @@
         <v>32</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>132</v>
-      </c>
       <c r="F15" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J15" s="7" t="s">
-        <v>134</v>
-      </c>
       <c r="K15" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N15" s="10"/>
       <c r="T15" s="10"/>
       <c r="V15" s="10" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="W15" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X15" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X15" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y15" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z15" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="45" x14ac:dyDescent="0.25">
@@ -3912,50 +3912,50 @@
         <v>32</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>137</v>
-      </c>
       <c r="F16" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="J16" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="K16" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N16" s="10"/>
       <c r="T16" s="10"/>
       <c r="V16" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="W16" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X16" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y16" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z16" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -3966,50 +3966,50 @@
         <v>32</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>142</v>
-      </c>
       <c r="F17" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J17" s="7" t="s">
-        <v>144</v>
-      </c>
       <c r="K17" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N17" s="10"/>
       <c r="T17" s="10"/>
       <c r="V17" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="W17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X17" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X17" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y17" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z17" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -4020,50 +4020,50 @@
         <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>147</v>
-      </c>
       <c r="F18" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="K18" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N18" s="10"/>
       <c r="T18" s="10"/>
       <c r="V18" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="W18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X18" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X18" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y18" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z18" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4074,50 +4074,50 @@
         <v>32</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="K19" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="L19" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" s="10"/>
       <c r="T19" s="10"/>
       <c r="V19" s="10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="W19" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X19" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="X19" s="10" t="s">
-        <v>119</v>
-      </c>
       <c r="Y19" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z19" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="150" x14ac:dyDescent="0.25">
@@ -4128,59 +4128,59 @@
         <v>32</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="E20" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>158</v>
-      </c>
       <c r="F20" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="M20" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="M20" s="10" t="s">
+      <c r="N20" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="N20" s="10" t="s">
+      <c r="T20" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="T20" s="10" t="s">
+      <c r="V20" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="W20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z20" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="W20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X20" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y20" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z20" s="11" t="s">
-        <v>165</v>
-      </c>
       <c r="AB20" s="14" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AD20" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -4191,62 +4191,62 @@
         <v>32</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>168</v>
-      </c>
       <c r="F21" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
       <c r="J21" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="K21" s="7" t="s">
+      <c r="L21" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="L21" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="M21" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="N21" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="P21" s="14" t="s">
         <v>672</v>
-      </c>
-      <c r="N21" s="14" t="s">
-        <v>674</v>
-      </c>
-      <c r="P21" s="14" t="s">
-        <v>673</v>
       </c>
       <c r="T21" s="10"/>
       <c r="W21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z21" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA21" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="X21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z21" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA21" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="AB21" s="14" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AD21" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
@@ -4257,19 +4257,19 @@
         <v>32</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="E22" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="F22" s="7" t="s">
+      <c r="G22" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -4277,21 +4277,21 @@
       <c r="K22" s="7"/>
       <c r="L22" s="8"/>
       <c r="M22" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N22" s="10"/>
       <c r="T22" s="10"/>
       <c r="W22" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X22" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y22" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z22" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="120" x14ac:dyDescent="0.25">
@@ -4302,13 +4302,13 @@
         <v>32</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>180</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>181</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>36</v>
@@ -4320,43 +4320,43 @@
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23" s="14" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="N23" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="P23" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="P23" s="10" t="s">
-        <v>679</v>
-      </c>
       <c r="T23" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="V23" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="W23" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X23" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y23" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z23" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA23" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB23" s="14" t="s">
+        <v>690</v>
+      </c>
+      <c r="AC23" s="10" t="s">
         <v>689</v>
       </c>
-      <c r="W23" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X23" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y23" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z23" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA23" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB23" s="14" t="s">
-        <v>691</v>
-      </c>
-      <c r="AC23" s="10" t="s">
-        <v>690</v>
-      </c>
       <c r="AD23" s="10" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="150" x14ac:dyDescent="0.25">
@@ -4367,47 +4367,47 @@
         <v>32</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>185</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="M24" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="T24" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="W24" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X24" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z24" s="11" t="s">
         <v>187</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="T24" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="W24" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X24" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y24" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z24" s="11" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -4418,16 +4418,16 @@
         <v>32</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>191</v>
-      </c>
       <c r="F25" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
@@ -4435,31 +4435,31 @@
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="M25" s="10" t="s">
+      <c r="N25" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="N25" s="10" t="s">
+      <c r="T25" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="V25" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="V25" s="10" t="s">
-        <v>196</v>
-      </c>
       <c r="W25" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X25" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y25" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z25" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -4470,57 +4470,57 @@
         <v>32</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="E26" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>199</v>
-      </c>
       <c r="F26" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="K26" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="L26" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L26" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="M26" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N26" s="10"/>
       <c r="T26" s="10"/>
       <c r="W26" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X26" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y26" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z26" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA26" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AB26" s="14" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AC26" s="10" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AD26" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -4531,47 +4531,47 @@
         <v>32</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="F27" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>206</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>207</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="L27" s="8"/>
       <c r="M27" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="N27" s="10" t="s">
         <v>210</v>
-      </c>
-      <c r="N27" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="T27" s="10"/>
       <c r="W27" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X27" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y27" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z27" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4582,16 +4582,16 @@
         <v>32</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>213</v>
-      </c>
       <c r="E28" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
@@ -4599,24 +4599,24 @@
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="N28" s="10"/>
       <c r="T28" s="10"/>
       <c r="W28" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y28" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="Y28" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="Z28" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.25">
@@ -4627,47 +4627,47 @@
         <v>32</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="E29" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="L29" s="8"/>
       <c r="M29" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="T29" s="10"/>
       <c r="W29" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X29" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X29" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y29" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z29" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -4678,16 +4678,16 @@
         <v>32</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>222</v>
-      </c>
       <c r="E30" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -4695,24 +4695,24 @@
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N30" s="10"/>
       <c r="T30" s="10"/>
       <c r="W30" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X30" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y30" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="Y30" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="Z30" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.25">
@@ -4723,47 +4723,47 @@
         <v>32</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="E31" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>226</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>227</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
       <c r="J31" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K31" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="L31" s="8"/>
       <c r="M31" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="N31" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="N31" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="T31" s="10"/>
       <c r="W31" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X31" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X31" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y31" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z31" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.25">
@@ -4774,50 +4774,50 @@
         <v>32</v>
       </c>
       <c r="C32" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="E32" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>232</v>
-      </c>
       <c r="F32" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>208</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>209</v>
       </c>
       <c r="L32" s="8"/>
       <c r="M32" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="N32" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="N32" s="10" t="s">
-        <v>234</v>
       </c>
       <c r="T32" s="10"/>
       <c r="V32" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="W32" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X32" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y32" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z32" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="W32" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X32" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y32" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z32" s="11" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -4828,16 +4828,16 @@
         <v>32</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>238</v>
-      </c>
       <c r="E33" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
@@ -4845,24 +4845,24 @@
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
       <c r="L33" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N33" s="10"/>
       <c r="T33" s="10"/>
       <c r="W33" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y33" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="Y33" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="Z33" s="11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
@@ -4873,19 +4873,19 @@
         <v>32</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="F34" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>242</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>243</v>
       </c>
       <c r="H34" s="7"/>
       <c r="I34" s="7"/>
@@ -4893,23 +4893,23 @@
       <c r="K34" s="7"/>
       <c r="L34" s="8"/>
       <c r="M34" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="N34" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="N34" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="T34" s="10"/>
       <c r="W34" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X34" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X34" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y34" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z34" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -4920,16 +4920,16 @@
         <v>32</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>247</v>
-      </c>
       <c r="E35" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -4938,23 +4938,23 @@
       <c r="K35" s="7"/>
       <c r="L35" s="8"/>
       <c r="M35" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="N35" s="10" t="s">
         <v>244</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>245</v>
       </c>
       <c r="T35" s="10"/>
       <c r="W35" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y35" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="Y35" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="Z35" s="11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -4965,52 +4965,52 @@
         <v>32</v>
       </c>
       <c r="C36" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D36" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="E36" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="F36" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>251</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>252</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="K36" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>254</v>
       </c>
       <c r="L36" s="8"/>
       <c r="M36" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="N36" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="N36" s="10" t="s">
+      <c r="T36" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="T36" s="10" t="s">
+      <c r="V36" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="V36" s="9" t="s">
+      <c r="W36" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y36" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z36" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="W36" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X36" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y36" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z36" s="11" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
@@ -5021,50 +5021,50 @@
         <v>32</v>
       </c>
       <c r="C37" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>262</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7"/>
       <c r="J37" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="K37" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>254</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="N37" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>264</v>
       </c>
       <c r="T37" s="10"/>
       <c r="V37" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="W37" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X37" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X37" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y37" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z37" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
@@ -5075,50 +5075,50 @@
         <v>32</v>
       </c>
       <c r="C38" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="F38" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>268</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>269</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="N38" s="10" t="s">
         <v>271</v>
-      </c>
-      <c r="N38" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="T38" s="10"/>
       <c r="V38" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="W38" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X38" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z38" s="11" t="s">
         <v>273</v>
-      </c>
-      <c r="W38" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X38" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y38" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z38" s="11" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="39" spans="1:29" ht="90" x14ac:dyDescent="0.25">
@@ -5129,50 +5129,50 @@
         <v>32</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>278</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>279</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="N39" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="N39" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="T39" s="10"/>
       <c r="V39" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="W39" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z39" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="W39" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X39" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y39" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z39" s="11" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5183,16 +5183,16 @@
         <v>32</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="E40" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="F40" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
@@ -5200,21 +5200,21 @@
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
       <c r="L40" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N40" s="10"/>
       <c r="T40" s="10"/>
       <c r="W40" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X40" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X40" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y40" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z40" s="11">
         <v>2</v>
@@ -5228,19 +5228,19 @@
         <v>32</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D41" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="E41" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
@@ -5248,27 +5248,27 @@
       <c r="K41" s="7"/>
       <c r="L41" s="8"/>
       <c r="M41" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N41" s="10"/>
       <c r="T41" s="10"/>
       <c r="W41" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X41" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y41" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z41" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC41" s="10" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.25">
@@ -5279,19 +5279,19 @@
         <v>32</v>
       </c>
       <c r="C42" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D42" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="E42" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>294</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
@@ -5299,23 +5299,23 @@
       <c r="K42" s="7"/>
       <c r="L42" s="8"/>
       <c r="M42" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="N42" s="10" t="s">
         <v>295</v>
-      </c>
-      <c r="N42" s="10" t="s">
-        <v>296</v>
       </c>
       <c r="T42" s="10"/>
       <c r="W42" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X42" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X42" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y42" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z42" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
@@ -5326,19 +5326,19 @@
         <v>32</v>
       </c>
       <c r="C43" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="E43" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G43" s="7" t="s">
         <v>298</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>299</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
@@ -5346,23 +5346,23 @@
       <c r="K43" s="7"/>
       <c r="L43" s="8"/>
       <c r="M43" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="N43" s="10" t="s">
         <v>300</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>301</v>
       </c>
       <c r="T43" s="10"/>
       <c r="W43" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X43" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X43" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y43" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z43" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:29" x14ac:dyDescent="0.25">
@@ -5373,19 +5373,19 @@
         <v>32</v>
       </c>
       <c r="C44" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="D44" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>303</v>
-      </c>
       <c r="E44" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
@@ -5393,23 +5393,23 @@
       <c r="K44" s="7"/>
       <c r="L44" s="8"/>
       <c r="M44" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="N44" s="10" t="s">
         <v>304</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>305</v>
       </c>
       <c r="T44" s="10"/>
       <c r="W44" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X44" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X44" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y44" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z44" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:29" x14ac:dyDescent="0.25">
@@ -5420,19 +5420,19 @@
         <v>32</v>
       </c>
       <c r="C45" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="D45" s="7" t="s">
-        <v>307</v>
-      </c>
       <c r="E45" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
@@ -5440,23 +5440,23 @@
       <c r="K45" s="7"/>
       <c r="L45" s="8"/>
       <c r="M45" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="N45" s="10" t="s">
         <v>308</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>309</v>
       </c>
       <c r="T45" s="10"/>
       <c r="W45" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X45" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X45" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y45" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z45" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
@@ -5467,48 +5467,48 @@
         <v>32</v>
       </c>
       <c r="C46" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D46" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>311</v>
-      </c>
       <c r="E46" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7"/>
       <c r="J46" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="8"/>
       <c r="M46" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="N46" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="N46" s="10" t="s">
-        <v>314</v>
       </c>
       <c r="T46" s="10"/>
       <c r="V46" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="W46" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X46" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y46" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z46" s="11" t="s">
         <v>315</v>
-      </c>
-      <c r="W46" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X46" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y46" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z46" s="11" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.25">
@@ -5519,19 +5519,19 @@
         <v>32</v>
       </c>
       <c r="C47" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="D47" s="7" t="s">
-        <v>318</v>
-      </c>
       <c r="E47" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H47" s="7"/>
       <c r="I47" s="7"/>
@@ -5539,23 +5539,23 @@
       <c r="K47" s="7"/>
       <c r="L47" s="8"/>
       <c r="M47" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="N47" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="N47" s="10" t="s">
-        <v>320</v>
       </c>
       <c r="T47" s="10"/>
       <c r="W47" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X47" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X47" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y47" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z47" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
@@ -5566,19 +5566,19 @@
         <v>32</v>
       </c>
       <c r="C48" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D48" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="E48" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>322</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>323</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7"/>
@@ -5586,28 +5586,28 @@
       <c r="K48" s="7"/>
       <c r="L48" s="8"/>
       <c r="M48" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="N48" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="N48" s="10" t="s">
+      <c r="T48" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="T48" s="10" t="s">
+      <c r="W48" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y48" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z48" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="W48" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X48" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y48" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z48" s="12" t="s">
+      <c r="AA48" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="AA48" s="10" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5618,49 +5618,49 @@
         <v>32</v>
       </c>
       <c r="C49" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D49" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="E49" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>331</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7"/>
       <c r="J49" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="K49" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="N49" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="N49" s="10" t="s">
+      <c r="T49" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="T49" s="10" t="s">
+      <c r="W49" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y49" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z49" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="W49" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X49" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y49" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z49" s="11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -5671,49 +5671,49 @@
         <v>32</v>
       </c>
       <c r="C50" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D50" s="7" t="s">
-        <v>339</v>
-      </c>
       <c r="E50" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
       <c r="K50" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="L50" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="L50" s="8" t="s">
-        <v>341</v>
-      </c>
       <c r="M50" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N50" s="10"/>
       <c r="T50" s="10"/>
       <c r="W50" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X50" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y50" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z50" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA50" s="10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AC50" s="10" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5724,52 +5724,52 @@
         <v>32</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D51" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="D51" s="7" t="s">
-        <v>344</v>
-      </c>
       <c r="E51" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7"/>
       <c r="J51" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="K51" s="7" t="s">
         <v>345</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>346</v>
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="N51" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="N51" s="10" t="s">
+      <c r="T51" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="W51" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X51" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y51" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z51" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="T51" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="W51" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X51" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y51" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z51" s="12" t="s">
+      <c r="AA51" s="10" t="s">
         <v>349</v>
-      </c>
-      <c r="AA51" s="10" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5780,45 +5780,45 @@
         <v>32</v>
       </c>
       <c r="C52" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>352</v>
-      </c>
       <c r="E52" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
       <c r="J52" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="K52" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K52" s="7" t="s">
-        <v>354</v>
-      </c>
       <c r="L52" s="8" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M52" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N52" s="10"/>
       <c r="T52" s="10"/>
       <c r="W52" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X52" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y52" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z52" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5829,19 +5829,19 @@
         <v>32</v>
       </c>
       <c r="C53" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G53" s="7" t="s">
         <v>356</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>357</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -5849,28 +5849,28 @@
       <c r="K53" s="7"/>
       <c r="L53" s="8"/>
       <c r="M53" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="N53" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="N53" s="10" t="s">
+      <c r="T53" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="W53" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X53" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y53" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z53" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="T53" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="W53" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X53" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y53" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z53" s="12" t="s">
-        <v>360</v>
-      </c>
       <c r="AA53" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5881,55 +5881,55 @@
         <v>32</v>
       </c>
       <c r="C54" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="D54" s="7" t="s">
+      <c r="E54" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
       <c r="J54" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>364</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>365</v>
       </c>
       <c r="L54" s="8"/>
       <c r="M54" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="N54" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="N54" s="10" t="s">
-        <v>367</v>
-      </c>
       <c r="T54" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="W54" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="X54" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Y54" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Z54" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AA54" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AC54" s="10" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -5940,16 +5940,16 @@
         <v>32</v>
       </c>
       <c r="C55" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D55" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>369</v>
-      </c>
       <c r="E55" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
@@ -5957,37 +5957,37 @@
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
       <c r="L55" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="M55" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="M55" s="10" t="s">
+      <c r="N55" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="T55" s="10" t="s">
+        <v>695</v>
+      </c>
+      <c r="V55" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="W55" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X55" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y55" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z55" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA55" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="T55" s="10" t="s">
+      <c r="AC55" s="10" t="s">
         <v>696</v>
-      </c>
-      <c r="V55" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="W55" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="X55" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y55" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z55" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA55" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="AC55" s="10" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="56" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -5998,55 +5998,55 @@
         <v>32</v>
       </c>
       <c r="C56" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>374</v>
-      </c>
       <c r="E56" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
       <c r="I56" s="7"/>
       <c r="J56" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="K56" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="L56" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="M56" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="M56" s="10" t="s">
+      <c r="N56" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="N56" s="10" t="s">
+      <c r="T56" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="T56" s="10" t="s">
+      <c r="W56" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X56" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y56" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z56" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="W56" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X56" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y56" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z56" s="11" t="s">
-        <v>381</v>
-      </c>
       <c r="AB56" s="14" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="AD56" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -6057,54 +6057,54 @@
         <v>32</v>
       </c>
       <c r="C57" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="D57" s="7" t="s">
-        <v>383</v>
-      </c>
       <c r="E57" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
       <c r="I57" s="7"/>
       <c r="J57" s="7"/>
       <c r="K57" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L57" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M57" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="N57" s="10" t="s">
         <v>700</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>701</v>
       </c>
       <c r="T57" s="10"/>
       <c r="V57" s="10" t="s">
+        <v>716</v>
+      </c>
+      <c r="W57" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="X57" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y57" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z57" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA57" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="AC57" s="10" t="s">
         <v>717</v>
-      </c>
-      <c r="W57" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="X57" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y57" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z57" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA57" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="AC57" s="10" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="58" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6115,54 +6115,54 @@
         <v>32</v>
       </c>
       <c r="C58" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="E58" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>387</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>388</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7"/>
       <c r="J58" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="K58" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L58" s="8"/>
       <c r="M58" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N58" s="10"/>
       <c r="T58" s="10"/>
       <c r="W58" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X58" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y58" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z58" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB58" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AC58" s="10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AD58" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.25">
@@ -6173,19 +6173,19 @@
         <v>32</v>
       </c>
       <c r="C59" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="D59" s="7" t="s">
-        <v>391</v>
-      </c>
       <c r="E59" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F59" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G59" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7"/>
@@ -6193,21 +6193,21 @@
       <c r="K59" s="7"/>
       <c r="L59" s="8"/>
       <c r="M59" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N59" s="10"/>
       <c r="T59" s="10"/>
       <c r="W59" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X59" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y59" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z59" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="135" x14ac:dyDescent="0.25">
@@ -6218,43 +6218,43 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>393</v>
-      </c>
       <c r="E60" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="M60" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N60" s="10"/>
       <c r="T60" s="10"/>
       <c r="W60" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X60" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y60" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z60" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -6265,43 +6265,43 @@
         <v>32</v>
       </c>
       <c r="C61" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="E61" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>398</v>
-      </c>
       <c r="F61" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
       <c r="I61" s="7"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="L61" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="L61" s="8" t="s">
-        <v>400</v>
-      </c>
       <c r="M61" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N61" s="10"/>
       <c r="T61" s="10"/>
       <c r="W61" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X61" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y61" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z61" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6312,43 +6312,43 @@
         <v>32</v>
       </c>
       <c r="C62" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="D62" s="7" t="s">
-        <v>402</v>
-      </c>
       <c r="E62" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
       <c r="J62" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M62" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N62" s="10"/>
       <c r="T62" s="10"/>
       <c r="W62" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X62" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y62" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z62" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6359,16 +6359,16 @@
         <v>32</v>
       </c>
       <c r="C63" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>406</v>
-      </c>
       <c r="E63" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
@@ -6376,24 +6376,24 @@
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
       <c r="L63" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M63" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N63" s="10"/>
       <c r="T63" s="10"/>
       <c r="W63" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X63" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y63" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z63" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6404,16 +6404,16 @@
         <v>32</v>
       </c>
       <c r="C64" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D64" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="D64" s="7" t="s">
-        <v>408</v>
-      </c>
       <c r="E64" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
@@ -6421,24 +6421,24 @@
       <c r="J64" s="7"/>
       <c r="K64" s="7"/>
       <c r="L64" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M64" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N64" s="10"/>
       <c r="T64" s="10"/>
       <c r="W64" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X64" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y64" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z64" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:30" ht="165" x14ac:dyDescent="0.25">
@@ -6449,16 +6449,16 @@
         <v>32</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D65" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="E65" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>411</v>
-      </c>
       <c r="F65" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
@@ -6466,24 +6466,24 @@
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
       <c r="L65" s="8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M65" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N65" s="10"/>
       <c r="T65" s="10"/>
       <c r="W65" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X65" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y65" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z65" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6494,43 +6494,43 @@
         <v>32</v>
       </c>
       <c r="C66" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="E66" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>415</v>
-      </c>
       <c r="F66" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
       <c r="I66" s="7"/>
       <c r="J66" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M66" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N66" s="10"/>
       <c r="T66" s="10"/>
       <c r="W66" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X66" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y66" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z66" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -6541,43 +6541,43 @@
         <v>32</v>
       </c>
       <c r="C67" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="E67" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>418</v>
-      </c>
       <c r="F67" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
       <c r="I67" s="7"/>
       <c r="J67" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N67" s="10"/>
       <c r="T67" s="10"/>
       <c r="W67" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X67" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y67" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z67" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.25">
@@ -6588,43 +6588,43 @@
         <v>32</v>
       </c>
       <c r="C68" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>420</v>
-      </c>
       <c r="E68" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F68" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="G68" s="7" t="s">
         <v>176</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>177</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7"/>
       <c r="J68" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="8"/>
       <c r="M68" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N68" s="10"/>
       <c r="T68" s="10"/>
       <c r="W68" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X68" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y68" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z68" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -6635,16 +6635,16 @@
         <v>32</v>
       </c>
       <c r="C69" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D69" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="E69" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>423</v>
-      </c>
       <c r="F69" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
@@ -6652,24 +6652,24 @@
       <c r="J69" s="7"/>
       <c r="K69" s="7"/>
       <c r="L69" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M69" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N69" s="10"/>
       <c r="T69" s="10"/>
       <c r="W69" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X69" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y69" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z69" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -6680,61 +6680,61 @@
         <v>32</v>
       </c>
       <c r="C70" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="E70" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="E70" s="7" t="s">
-        <v>427</v>
-      </c>
       <c r="F70" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
       <c r="I70" s="7"/>
       <c r="J70" s="7"/>
       <c r="K70" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="L70" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="L70" s="8" t="s">
+      <c r="M70" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="M70" s="14" t="s">
-        <v>430</v>
-      </c>
       <c r="N70" s="10" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="S70" s="16"/>
       <c r="T70" s="14"/>
       <c r="W70" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X70" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y70" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z70" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA70" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AB70" s="14" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AC70" s="10" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AD70" s="10" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="71" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -6745,43 +6745,43 @@
         <v>32</v>
       </c>
       <c r="C71" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="D71" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="D71" s="7" t="s">
+      <c r="E71" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="E71" s="7" t="s">
-        <v>434</v>
-      </c>
       <c r="F71" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
       <c r="I71" s="7"/>
       <c r="J71" s="7"/>
       <c r="K71" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L71" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="M71" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N71" s="10"/>
       <c r="T71" s="10"/>
       <c r="W71" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X71" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y71" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z71" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:30" ht="180" x14ac:dyDescent="0.25">
@@ -6792,65 +6792,65 @@
         <v>32</v>
       </c>
       <c r="C72" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="D72" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="E72" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>438</v>
-      </c>
       <c r="F72" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
       <c r="I72" s="7"/>
       <c r="J72" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K72" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="L72" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M72" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="N72" s="10" t="s">
         <v>708</v>
       </c>
-      <c r="N72" s="10" t="s">
+      <c r="P72" s="10" t="s">
         <v>709</v>
       </c>
-      <c r="P72" s="10" t="s">
-        <v>710</v>
-      </c>
       <c r="T72" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="V72" s="14"/>
       <c r="W72" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X72" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y72" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z72" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA72" s="10" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AB72" s="14" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AC72" s="10" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AD72" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="73" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -6861,43 +6861,43 @@
         <v>32</v>
       </c>
       <c r="C73" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="D73" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="D73" s="7" t="s">
+      <c r="E73" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="E73" s="7" t="s">
-        <v>443</v>
-      </c>
       <c r="F73" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
       <c r="I73" s="7"/>
       <c r="J73" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M73" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N73" s="10"/>
       <c r="T73" s="10"/>
       <c r="W73" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X73" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y73" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z73" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -6908,49 +6908,49 @@
         <v>32</v>
       </c>
       <c r="C74" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="E74" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="E74" s="7" t="s">
-        <v>447</v>
-      </c>
       <c r="F74" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
       <c r="J74" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="K74" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="L74" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="M74" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="K74" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="L74" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="M74" s="10" t="s">
+      <c r="N74" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="N74" s="10" t="s">
+      <c r="T74" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="W74" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X74" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y74" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z74" s="11" t="s">
         <v>450</v>
-      </c>
-      <c r="T74" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="W74" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X74" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y74" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z74" s="11" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="75" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
@@ -6961,48 +6961,48 @@
         <v>32</v>
       </c>
       <c r="C75" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="D75" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="D75" s="7" t="s">
+      <c r="E75" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="E75" s="7" t="s">
-        <v>454</v>
-      </c>
       <c r="F75" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
       <c r="I75" s="7"/>
       <c r="J75" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="8"/>
       <c r="M75" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="N75" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="N75" s="10" t="s">
+      <c r="T75" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="T75" s="10" t="s">
+      <c r="W75" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X75" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y75" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="W75" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X75" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y75" s="10" t="s">
-        <v>459</v>
-      </c>
       <c r="Z75" s="11" t="s">
+        <v>723</v>
+      </c>
+      <c r="AC75" s="10" t="s">
         <v>724</v>
-      </c>
-      <c r="AC75" s="10" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="76" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
@@ -7013,19 +7013,19 @@
         <v>32</v>
       </c>
       <c r="C76" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="D76" s="7" t="s">
+      <c r="E76" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="F76" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G76" s="7" t="s">
         <v>462</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>463</v>
       </c>
       <c r="H76" s="7"/>
       <c r="I76" s="7"/>
@@ -7033,26 +7033,26 @@
       <c r="K76" s="7"/>
       <c r="L76" s="8"/>
       <c r="M76" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N76" s="10"/>
       <c r="T76" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="W76" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X76" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y76" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="W76" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X76" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y76" s="10" t="s">
-        <v>459</v>
-      </c>
       <c r="Z76" s="11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AC76" s="10" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="77" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -7063,47 +7063,47 @@
         <v>32</v>
       </c>
       <c r="C77" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D77" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="D77" s="7" t="s">
-        <v>465</v>
-      </c>
       <c r="E77" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7"/>
       <c r="J77" s="7"/>
       <c r="K77" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="L77" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="L77" s="8" t="s">
+      <c r="M77" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="M77" s="10" t="s">
+      <c r="N77" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="T77" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="N77" s="10" t="s">
-        <v>457</v>
-      </c>
-      <c r="T77" s="10" t="s">
+      <c r="W77" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X77" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y77" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z77" s="11" t="s">
         <v>469</v>
-      </c>
-      <c r="W77" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X77" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y77" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z77" s="11" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="78" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7114,55 +7114,55 @@
         <v>32</v>
       </c>
       <c r="C78" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D78" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="D78" s="7" t="s">
+      <c r="E78" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="E78" s="7" t="s">
-        <v>473</v>
-      </c>
       <c r="F78" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7"/>
       <c r="J78" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="K78" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="K78" s="7" t="s">
+      <c r="L78" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="L78" s="8" t="s">
+      <c r="M78" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="M78" s="10" t="s">
+      <c r="N78" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="T78" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="W78" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X78" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y78" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z78" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="N78" s="10" t="s">
-        <v>739</v>
-      </c>
-      <c r="T78" s="10" t="s">
+      <c r="AA78" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="AD78" s="9" t="s">
         <v>740</v>
-      </c>
-      <c r="W78" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X78" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y78" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z78" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="AA78" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="AD78" s="9" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="79" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7173,54 +7173,54 @@
         <v>32</v>
       </c>
       <c r="C79" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D79" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="D79" s="7" t="s">
+      <c r="E79" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="E79" s="7" t="s">
-        <v>482</v>
-      </c>
       <c r="F79" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="J79" s="7" t="s">
         <v>483</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>484</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M79" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N79" s="10"/>
       <c r="T79" s="10"/>
       <c r="W79" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X79" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y79" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z79" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA79" s="10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AB79" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AD79" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="80" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7231,58 +7231,58 @@
         <v>32</v>
       </c>
       <c r="C80" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D80" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="D80" s="7" t="s">
+      <c r="E80" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="E80" s="7" t="s">
-        <v>488</v>
-      </c>
       <c r="F80" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M80" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N80" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="T80" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="T80" s="10" t="s">
+      <c r="W80" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X80" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y80" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z80" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA80" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="W80" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X80" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y80" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z80" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA80" s="10" t="s">
-        <v>492</v>
-      </c>
       <c r="AB80" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AD80" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="81" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7293,58 +7293,58 @@
         <v>32</v>
       </c>
       <c r="C81" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D81" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="D81" s="7" t="s">
+      <c r="E81" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="E81" s="7" t="s">
-        <v>495</v>
-      </c>
       <c r="F81" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J81" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M81" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N81" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="T81" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="T81" s="10" t="s">
+      <c r="W81" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X81" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y81" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z81" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA81" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="W81" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X81" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y81" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z81" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA81" s="10" t="s">
-        <v>499</v>
-      </c>
       <c r="AB81" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AD81" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="82" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7355,58 +7355,58 @@
         <v>32</v>
       </c>
       <c r="C82" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D82" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="D82" s="7" t="s">
+      <c r="E82" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="E82" s="7" t="s">
-        <v>502</v>
-      </c>
       <c r="F82" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J82" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M82" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N82" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="T82" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="W82" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X82" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y82" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z82" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA82" s="10" t="s">
         <v>504</v>
       </c>
-      <c r="T82" s="15" t="s">
-        <v>491</v>
-      </c>
-      <c r="W82" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X82" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y82" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z82" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA82" s="10" t="s">
-        <v>505</v>
-      </c>
       <c r="AB82" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AD82" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="83" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7417,45 +7417,45 @@
         <v>32</v>
       </c>
       <c r="C83" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="D83" s="7" t="s">
+      <c r="E83" s="7" t="s">
         <v>507</v>
       </c>
-      <c r="E83" s="7" t="s">
-        <v>508</v>
-      </c>
       <c r="F83" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="7" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M83" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N83" s="10"/>
       <c r="T83" s="10"/>
       <c r="W83" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X83" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y83" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z83" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7466,49 +7466,49 @@
         <v>32</v>
       </c>
       <c r="C84" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="D84" s="7" t="s">
+      <c r="E84" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="E84" s="7" t="s">
-        <v>512</v>
-      </c>
       <c r="F84" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M84" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="N84" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="N84" s="10" t="s">
+      <c r="T84" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="T84" s="10" t="s">
-        <v>516</v>
-      </c>
       <c r="W84" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X84" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X84" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y84" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z84" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="85" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7519,53 +7519,53 @@
         <v>32</v>
       </c>
       <c r="C85" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="E85" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="E85" s="7" t="s">
-        <v>519</v>
-      </c>
       <c r="F85" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="K85" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="K85" s="7" t="s">
-        <v>522</v>
-      </c>
       <c r="L85" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M85" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N85" s="10"/>
       <c r="T85" s="10"/>
       <c r="W85" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X85" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y85" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z85" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB85" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD85" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="86" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7576,58 +7576,58 @@
         <v>32</v>
       </c>
       <c r="C86" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="E86" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="E86" s="7" t="s">
-        <v>525</v>
-      </c>
       <c r="F86" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M86" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N86" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="T86" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="T86" s="10" t="s">
+      <c r="W86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA86" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="W86" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X86" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y86" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z86" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA86" s="10" t="s">
-        <v>529</v>
-      </c>
       <c r="AB86" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD86" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="87" spans="1:30" ht="90" x14ac:dyDescent="0.25">
@@ -7638,50 +7638,50 @@
         <v>32</v>
       </c>
       <c r="C87" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="E87" s="7" t="s">
-        <v>532</v>
-      </c>
       <c r="F87" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M87" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="N87" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="T87" s="10" t="s">
         <v>535</v>
       </c>
-      <c r="T87" s="10" t="s">
+      <c r="V87" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="V87" s="10" t="s">
+      <c r="W87" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X87" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y87" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z87" s="11" t="s">
         <v>537</v>
-      </c>
-      <c r="W87" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X87" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y87" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z87" s="11" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="88" spans="1:30" ht="105" x14ac:dyDescent="0.25">
@@ -7692,51 +7692,51 @@
         <v>32</v>
       </c>
       <c r="C88" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="D88" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="D88" s="7" t="s">
+      <c r="E88" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="E88" s="7" t="s">
-        <v>541</v>
-      </c>
       <c r="F88" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="K88" s="7" t="s">
         <v>542</v>
       </c>
-      <c r="J88" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="K88" s="7" t="s">
+      <c r="L88" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="M88" s="10" t="s">
         <v>543</v>
       </c>
-      <c r="L88" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="M88" s="10" t="s">
+      <c r="N88" s="10" t="s">
         <v>544</v>
       </c>
-      <c r="N88" s="10" t="s">
+      <c r="T88" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="T88" s="10" t="s">
+      <c r="W88" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X88" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y88" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z88" s="11" t="s">
         <v>546</v>
-      </c>
-      <c r="W88" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X88" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y88" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z88" s="11" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="89" spans="1:30" ht="105" x14ac:dyDescent="0.25">
@@ -7747,47 +7747,47 @@
         <v>32</v>
       </c>
       <c r="C89" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="D89" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="D89" s="7" t="s">
-        <v>549</v>
-      </c>
       <c r="E89" s="7" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="L89" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="L89" s="8" t="s">
+      <c r="M89" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="N89" s="10" t="s">
+        <v>544</v>
+      </c>
+      <c r="T89" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="W89" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X89" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y89" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z89" s="11" t="s">
         <v>551</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>544</v>
-      </c>
-      <c r="N89" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="T89" s="10" t="s">
-        <v>546</v>
-      </c>
-      <c r="W89" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X89" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y89" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z89" s="11" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="90" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7798,58 +7798,58 @@
         <v>32</v>
       </c>
       <c r="C90" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="D90" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="D90" s="7" t="s">
+      <c r="E90" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="E90" s="7" t="s">
-        <v>555</v>
-      </c>
       <c r="F90" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="K90" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="K90" s="7" t="s">
+      <c r="L90" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="M90" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N90" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="L90" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="M90" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="N90" s="10" t="s">
+      <c r="T90" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="T90" s="10" t="s">
+      <c r="W90" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X90" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y90" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z90" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA90" s="10" t="s">
         <v>559</v>
       </c>
-      <c r="W90" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X90" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y90" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z90" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA90" s="10" t="s">
-        <v>560</v>
-      </c>
       <c r="AB90" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD90" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="91" spans="1:30" ht="60" x14ac:dyDescent="0.25">
@@ -7860,55 +7860,55 @@
         <v>32</v>
       </c>
       <c r="C91" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="D91" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="D91" s="7" t="s">
+      <c r="E91" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="E91" s="7" t="s">
-        <v>563</v>
-      </c>
       <c r="F91" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M91" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N91" s="10"/>
       <c r="T91" s="10"/>
       <c r="W91" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X91" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y91" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z91" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AA91" s="10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AB91" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AC91" s="10" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AD91" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="92" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7919,49 +7919,49 @@
         <v>32</v>
       </c>
       <c r="C92" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D92" s="7" t="s">
+      <c r="E92" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="E92" s="7" t="s">
-        <v>568</v>
-      </c>
       <c r="F92" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M92" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N92" s="10"/>
       <c r="T92" s="10"/>
       <c r="W92" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X92" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y92" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z92" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB92" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD92" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="93" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -7972,49 +7972,49 @@
         <v>32</v>
       </c>
       <c r="C93" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="D93" s="7" t="s">
         <v>569</v>
       </c>
-      <c r="D93" s="7" t="s">
+      <c r="E93" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="E93" s="7" t="s">
-        <v>571</v>
-      </c>
       <c r="F93" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N93" s="10"/>
       <c r="T93" s="10"/>
       <c r="W93" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X93" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y93" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z93" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB93" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD93" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="94" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8025,49 +8025,49 @@
         <v>32</v>
       </c>
       <c r="C94" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="D94" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="D94" s="7" t="s">
+      <c r="E94" s="7" t="s">
         <v>573</v>
       </c>
-      <c r="E94" s="7" t="s">
-        <v>574</v>
-      </c>
       <c r="F94" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M94" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N94" s="10"/>
       <c r="T94" s="10"/>
       <c r="W94" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X94" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y94" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z94" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB94" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD94" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="95" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8078,49 +8078,49 @@
         <v>32</v>
       </c>
       <c r="C95" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="D95" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="D95" s="7" t="s">
+      <c r="E95" s="7" t="s">
         <v>576</v>
       </c>
-      <c r="E95" s="7" t="s">
-        <v>577</v>
-      </c>
       <c r="F95" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M95" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N95" s="10"/>
       <c r="T95" s="10"/>
       <c r="W95" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X95" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y95" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z95" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB95" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD95" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="96" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8131,49 +8131,49 @@
         <v>32</v>
       </c>
       <c r="C96" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="D96" s="7" t="s">
+      <c r="E96" s="7" t="s">
         <v>579</v>
       </c>
-      <c r="E96" s="7" t="s">
-        <v>580</v>
-      </c>
       <c r="F96" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M96" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N96" s="10"/>
       <c r="T96" s="10"/>
       <c r="W96" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X96" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y96" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z96" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB96" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD96" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="97" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8184,49 +8184,49 @@
         <v>32</v>
       </c>
       <c r="C97" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="D97" s="7" t="s">
         <v>581</v>
       </c>
-      <c r="D97" s="7" t="s">
+      <c r="E97" s="7" t="s">
         <v>582</v>
       </c>
-      <c r="E97" s="7" t="s">
-        <v>583</v>
-      </c>
       <c r="F97" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M97" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N97" s="10"/>
       <c r="T97" s="10"/>
       <c r="W97" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X97" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y97" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z97" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB97" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD97" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="98" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8237,49 +8237,49 @@
         <v>32</v>
       </c>
       <c r="C98" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="D98" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="D98" s="7" t="s">
+      <c r="E98" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>586</v>
-      </c>
       <c r="F98" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M98" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N98" s="10"/>
       <c r="T98" s="10"/>
       <c r="W98" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X98" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y98" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z98" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB98" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD98" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="99" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8290,49 +8290,49 @@
         <v>32</v>
       </c>
       <c r="C99" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="D99" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="D99" s="7" t="s">
+      <c r="E99" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="E99" s="7" t="s">
-        <v>589</v>
-      </c>
       <c r="F99" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N99" s="10"/>
       <c r="T99" s="10"/>
       <c r="W99" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X99" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y99" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z99" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB99" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD99" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="100" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8343,49 +8343,49 @@
         <v>32</v>
       </c>
       <c r="C100" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="D100" s="7" t="s">
+      <c r="E100" s="7" t="s">
         <v>591</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>592</v>
-      </c>
       <c r="F100" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M100" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N100" s="10"/>
       <c r="T100" s="10"/>
       <c r="W100" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X100" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y100" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z100" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB100" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD100" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="101" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8396,56 +8396,56 @@
         <v>32</v>
       </c>
       <c r="C101" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="D101" s="7" t="s">
         <v>593</v>
       </c>
-      <c r="D101" s="7" t="s">
+      <c r="E101" s="7" t="s">
         <v>594</v>
       </c>
-      <c r="E101" s="7" t="s">
-        <v>595</v>
-      </c>
       <c r="F101" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M101" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N101" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="T101" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="W101" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X101" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y101" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z101" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA101" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="T101" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="W101" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="X101" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y101" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="Z101" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA101" s="10" t="s">
-        <v>597</v>
-      </c>
       <c r="AB101" s="14" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AD101" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="102" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8456,49 +8456,49 @@
         <v>32</v>
       </c>
       <c r="C102" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="D102" s="7" t="s">
         <v>598</v>
       </c>
-      <c r="D102" s="7" t="s">
+      <c r="E102" s="7" t="s">
         <v>599</v>
       </c>
-      <c r="E102" s="7" t="s">
-        <v>600</v>
-      </c>
       <c r="F102" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M102" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N102" s="10"/>
       <c r="T102" s="10"/>
       <c r="W102" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X102" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y102" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z102" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB102" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD102" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="103" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8509,49 +8509,49 @@
         <v>32</v>
       </c>
       <c r="C103" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="D103" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="D103" s="7" t="s">
+      <c r="E103" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="E103" s="7" t="s">
-        <v>603</v>
-      </c>
       <c r="F103" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M103" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N103" s="10"/>
       <c r="T103" s="10"/>
       <c r="W103" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X103" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y103" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z103" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB103" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD103" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="104" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8562,49 +8562,49 @@
         <v>32</v>
       </c>
       <c r="C104" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="D104" s="7" t="s">
         <v>604</v>
       </c>
-      <c r="D104" s="7" t="s">
+      <c r="E104" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="E104" s="7" t="s">
-        <v>606</v>
-      </c>
       <c r="F104" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M104" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N104" s="10"/>
       <c r="T104" s="10"/>
       <c r="W104" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X104" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y104" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z104" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB104" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD104" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="105" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8615,49 +8615,49 @@
         <v>32</v>
       </c>
       <c r="C105" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="D105" s="7" t="s">
         <v>607</v>
       </c>
-      <c r="D105" s="7" t="s">
+      <c r="E105" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="E105" s="7" t="s">
-        <v>609</v>
-      </c>
       <c r="F105" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M105" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N105" s="10"/>
       <c r="T105" s="10"/>
       <c r="W105" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X105" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y105" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z105" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB105" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD105" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="106" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8668,49 +8668,49 @@
         <v>32</v>
       </c>
       <c r="C106" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>610</v>
       </c>
-      <c r="D106" s="7" t="s">
+      <c r="E106" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="E106" s="7" t="s">
-        <v>612</v>
-      </c>
       <c r="F106" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M106" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N106" s="10"/>
       <c r="T106" s="10"/>
       <c r="W106" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X106" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y106" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z106" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB106" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD106" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="107" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8721,49 +8721,49 @@
         <v>32</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D107" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="D107" s="7" t="s">
+      <c r="E107" s="7" t="s">
         <v>614</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>615</v>
-      </c>
       <c r="F107" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M107" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N107" s="10"/>
       <c r="T107" s="10"/>
       <c r="W107" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X107" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y107" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z107" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB107" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD107" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="108" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8774,49 +8774,49 @@
         <v>32</v>
       </c>
       <c r="C108" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="D108" s="7" t="s">
         <v>616</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="E108" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="E108" s="7" t="s">
-        <v>618</v>
-      </c>
       <c r="F108" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M108" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N108" s="10"/>
       <c r="T108" s="10"/>
       <c r="W108" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X108" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y108" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z108" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB108" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD108" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="109" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8827,49 +8827,49 @@
         <v>32</v>
       </c>
       <c r="C109" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="D109" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="D109" s="7" t="s">
+      <c r="E109" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="E109" s="7" t="s">
-        <v>621</v>
-      </c>
       <c r="F109" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M109" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N109" s="10"/>
       <c r="T109" s="10"/>
       <c r="W109" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X109" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y109" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Z109" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB109" s="14" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AD109" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="110" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8880,43 +8880,43 @@
         <v>32</v>
       </c>
       <c r="C110" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D110" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="E110" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="E110" s="7" t="s">
-        <v>624</v>
-      </c>
       <c r="F110" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M110" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N110" s="10"/>
       <c r="T110" s="10"/>
       <c r="W110" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X110" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y110" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z110" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="111" spans="1:30" ht="75" x14ac:dyDescent="0.25">
@@ -8927,54 +8927,54 @@
         <v>32</v>
       </c>
       <c r="C111" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="D111" s="7" t="s">
         <v>626</v>
       </c>
-      <c r="D111" s="7" t="s">
+      <c r="E111" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="E111" s="7" t="s">
-        <v>628</v>
-      </c>
       <c r="F111" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M111" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N111" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="P111" s="10" t="s">
         <v>715</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>716</v>
       </c>
       <c r="T111" s="10"/>
       <c r="W111" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="X111" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="X111" s="14" t="s">
-        <v>119</v>
-      </c>
       <c r="Y111" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z111" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AA111" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AC111" s="14" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="112" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -8985,43 +8985,43 @@
         <v>32</v>
       </c>
       <c r="C112" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D112" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="E112" s="7" t="s">
         <v>632</v>
       </c>
-      <c r="E112" s="7" t="s">
-        <v>633</v>
-      </c>
       <c r="F112" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M112" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N112" s="10"/>
       <c r="T112" s="10"/>
       <c r="W112" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X112" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y112" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z112" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9032,47 +9032,47 @@
         <v>32</v>
       </c>
       <c r="C113" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="D113" s="7" t="s">
         <v>634</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>635</v>
-      </c>
       <c r="E113" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M113" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="N113" s="10" t="s">
         <v>637</v>
       </c>
-      <c r="N113" s="10" t="s">
-        <v>638</v>
-      </c>
       <c r="T113" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="W113" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X113" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X113" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y113" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z113" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9083,47 +9083,47 @@
         <v>32</v>
       </c>
       <c r="C114" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="D114" s="7" t="s">
         <v>639</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>640</v>
-      </c>
       <c r="E114" s="7" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M114" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="N114" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="N114" s="10" t="s">
-        <v>643</v>
-      </c>
       <c r="T114" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="W114" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X114" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X114" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y114" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z114" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115" spans="1:27" ht="45" x14ac:dyDescent="0.25">
@@ -9134,47 +9134,47 @@
         <v>32</v>
       </c>
       <c r="C115" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="D115" s="7" t="s">
         <v>644</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>645</v>
-      </c>
       <c r="E115" s="7" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="8" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M115" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="N115" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="N115" s="10" t="s">
-        <v>647</v>
-      </c>
       <c r="T115" s="10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="W115" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X115" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="X115" s="10" t="s">
-        <v>40</v>
-      </c>
       <c r="Y115" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Z115" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" spans="1:27" x14ac:dyDescent="0.25">
@@ -9185,41 +9185,41 @@
         <v>32</v>
       </c>
       <c r="C116" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="D116" s="7" t="s">
         <v>648</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>649</v>
-      </c>
       <c r="E116" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="8"/>
       <c r="M116" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N116" s="10"/>
       <c r="T116" s="10"/>
       <c r="W116" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X116" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y116" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z116" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:27" x14ac:dyDescent="0.25">
@@ -9230,41 +9230,41 @@
         <v>32</v>
       </c>
       <c r="C117" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="D117" s="7" t="s">
         <v>651</v>
       </c>
-      <c r="D117" s="7" t="s">
-        <v>652</v>
-      </c>
       <c r="E117" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="8"/>
       <c r="M117" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N117" s="10"/>
       <c r="T117" s="10"/>
       <c r="W117" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X117" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y117" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z117" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:27" x14ac:dyDescent="0.25">
@@ -9275,41 +9275,41 @@
         <v>32</v>
       </c>
       <c r="C118" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="D118" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="D118" s="7" t="s">
-        <v>655</v>
-      </c>
       <c r="E118" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="8"/>
       <c r="M118" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N118" s="10"/>
       <c r="T118" s="10"/>
       <c r="W118" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X118" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y118" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z118" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:27" x14ac:dyDescent="0.25">
@@ -9320,41 +9320,41 @@
         <v>32</v>
       </c>
       <c r="C119" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="D119" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="D119" s="7" t="s">
-        <v>658</v>
-      </c>
       <c r="E119" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="8"/>
       <c r="M119" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N119" s="10"/>
       <c r="T119" s="10"/>
       <c r="W119" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X119" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y119" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z119" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" spans="1:27" ht="375" x14ac:dyDescent="0.25">
@@ -9365,48 +9365,48 @@
         <v>32</v>
       </c>
       <c r="C120" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="D120" s="7" t="s">
         <v>660</v>
       </c>
-      <c r="D120" s="7" t="s">
-        <v>661</v>
-      </c>
       <c r="E120" s="7" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="8"/>
       <c r="M120" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="N120" s="10" t="s">
         <v>663</v>
       </c>
-      <c r="N120" s="10" t="s">
+      <c r="T120" s="10" t="s">
         <v>664</v>
       </c>
-      <c r="T120" s="10" t="s">
+      <c r="W120" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="X120" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y120" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="Z120" s="12" t="s">
         <v>665</v>
       </c>
-      <c r="W120" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="X120" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y120" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="Z120" s="12" t="s">
+      <c r="AA120" s="10" t="s">
         <v>666</v>
-      </c>
-      <c r="AA120" s="10" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="121" spans="1:27" x14ac:dyDescent="0.25">
@@ -9417,41 +9417,41 @@
         <v>32</v>
       </c>
       <c r="C121" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="D121" s="7" t="s">
         <v>668</v>
       </c>
-      <c r="D121" s="7" t="s">
-        <v>669</v>
-      </c>
       <c r="E121" s="7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="8"/>
       <c r="M121" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N121" s="10"/>
       <c r="T121" s="10"/>
       <c r="W121" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X121" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y121" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z121" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="122" spans="1:27" x14ac:dyDescent="0.25">
@@ -9462,41 +9462,41 @@
         <v>32</v>
       </c>
       <c r="C122" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="D122" s="7" t="s">
         <v>670</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>671</v>
-      </c>
       <c r="E122" s="7" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="8"/>
       <c r="M122" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N122" s="10"/>
       <c r="T122" s="10"/>
       <c r="W122" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="X122" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Y122" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Z122" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/baseline/data_processing_elements-MSN.xlsx
+++ b/baseline/data_processing_elements-MSN.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\twey working files\ProPASS\MSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D814D6F9-E04B-4791-A9D9-2A5BBB89AA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A537D76-AEEB-43BD-A9C1-F17B018B0AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1729" uniqueCount="747">
   <si>
     <t>index</t>
   </si>
@@ -1708,9 +1708,6 @@
     <t>Acceptable wording is "atrial fibrillation".</t>
   </si>
   <si>
-    <t>Minnesota_Afib_comb</t>
-  </si>
-  <si>
     <t>Minnesota classification of atrial fibrillation (persistent and intermittent combined)</t>
   </si>
   <si>
@@ -1777,12 +1774,6 @@
 If the study-specific variable was collected as part of a select-all-that-apply section without a response option for No, the harmonized values can be Yes/Presumed no. Code as "Presumed no" if the item was not selected but at least one other item in the section was selected.</t>
   </si>
   <si>
-    <t>B5_MS22.3b.2;
-B5_MS22.3b.4;
-B5_MS22.3b.5;
-B5_MS22.3b.7</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ever diagnosed: osteoarthritis;
 Ever diagnosed: rheumatoid arthritis;
 Ever diagnosed: psoriatic arthritis;
@@ -1798,10 +1789,6 @@
   </si>
   <si>
     <t>The "No" could not be generated because no "Other" category or variable.</t>
-  </si>
-  <si>
-    <t>case_when(B5_MS22.3b.2 == 1 | B5_MS22.3b.4 == 1 | B5_MS22.3b.5 == 1 | B5_MS22.3b.7 == 1 ~ 1L;
-ELSE ~ NA)</t>
   </si>
   <si>
     <t>dis_diabetes_ever</t>
@@ -2584,6 +2571,20 @@
   </si>
   <si>
     <t>participant ID</t>
+  </si>
+  <si>
+    <t>Available, would need to request.</t>
+  </si>
+  <si>
+    <t>Input variable Minnesota_Afib_comb. Would be direct_mapping.</t>
+  </si>
+  <si>
+    <t>Available but need to request.</t>
+  </si>
+  <si>
+    <t>Input variables B5_MS22.3b.2; B5_MS22.3b.4; B5_MS22.3b.5; B5_MS22.3b.7 available. 
+case_when(B5_MS22.3b.2 == 1 | B5_MS22.3b.4 == 1 | B5_MS22.3b.5 == 1 | B5_MS22.3b.7 == 1 ~ 1L;
+ELSE ~ NA)</t>
   </si>
 </sst>
 </file>
@@ -3049,45 +3050,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG122"/>
-  <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="28.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5" style="9" customWidth="1"/>
     <col min="2" max="2" width="7" style="9" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" style="9" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.453125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.140625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="28.7109375" style="9" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.1796875" style="9" customWidth="1"/>
+    <col min="10" max="10" width="28.7265625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="18.453125" style="9" customWidth="1"/>
     <col min="12" max="12" width="37" style="10" customWidth="1"/>
-    <col min="13" max="13" width="33.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.7109375" style="9" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.140625" style="10" customWidth="1"/>
-    <col min="17" max="17" width="15.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="52.28515625" style="9" customWidth="1"/>
-    <col min="21" max="21" width="15.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="50.140625" style="10" customWidth="1"/>
-    <col min="23" max="23" width="21.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="27.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="28.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="33.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.7265625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="16.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="56.1796875" style="10" customWidth="1"/>
+    <col min="17" max="17" width="15.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="52.26953125" style="9" customWidth="1"/>
+    <col min="21" max="21" width="15.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="50.1796875" style="10" customWidth="1"/>
+    <col min="23" max="23" width="21.26953125" style="9" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.54296875" style="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.26953125" style="9" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="68" style="10" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="60.7109375" style="10" customWidth="1"/>
-    <col min="28" max="28" width="63.140625" style="10" customWidth="1"/>
-    <col min="29" max="29" width="60.7109375" style="10" customWidth="1"/>
+    <col min="27" max="27" width="60.7265625" style="10" customWidth="1"/>
+    <col min="28" max="28" width="63.1796875" style="10" customWidth="1"/>
+    <col min="29" max="29" width="60.7265625" style="10" customWidth="1"/>
     <col min="30" max="30" width="64" style="9" customWidth="1"/>
-    <col min="31" max="31" width="24.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="27.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="28.7109375" style="9"/>
+    <col min="31" max="31" width="24.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="27.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="24.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="28.7265625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3176,7 +3177,7 @@
         <v>28</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>29</v>
@@ -3188,7 +3189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -3216,10 +3217,10 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
       <c r="M2" s="10" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="T2" s="10"/>
       <c r="W2" s="10" t="s">
@@ -3232,10 +3233,10 @@
         <v>40</v>
       </c>
       <c r="Z2" s="11" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -3280,7 +3281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -3370,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -3424,7 +3425,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -3473,7 +3474,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>7</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="165" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>8</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="165" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>9</v>
       </c>
@@ -3627,13 +3628,13 @@
         <v>76</v>
       </c>
       <c r="Z10" s="11" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>10</v>
       </c>
@@ -3688,7 +3689,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>11</v>
       </c>
@@ -3727,7 +3728,7 @@
       <c r="N12" s="10"/>
       <c r="T12" s="10"/>
       <c r="V12" s="10" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="W12" s="10" t="s">
         <v>117</v>
@@ -3742,7 +3743,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>12</v>
       </c>
@@ -3781,7 +3782,7 @@
       <c r="N13" s="10"/>
       <c r="T13" s="10"/>
       <c r="V13" s="10" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>117</v>
@@ -3796,7 +3797,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>13</v>
       </c>
@@ -3835,7 +3836,7 @@
       <c r="N14" s="10"/>
       <c r="T14" s="10"/>
       <c r="V14" s="10" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="W14" s="10" t="s">
         <v>117</v>
@@ -3850,7 +3851,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>14</v>
       </c>
@@ -3889,7 +3890,7 @@
       <c r="N15" s="10"/>
       <c r="T15" s="10"/>
       <c r="V15" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="W15" s="10" t="s">
         <v>117</v>
@@ -3904,7 +3905,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:33" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>15</v>
       </c>
@@ -3943,7 +3944,7 @@
       <c r="N16" s="10"/>
       <c r="T16" s="10"/>
       <c r="V16" s="10" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="W16" s="10" t="s">
         <v>117</v>
@@ -3958,7 +3959,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>16</v>
       </c>
@@ -3997,7 +3998,7 @@
       <c r="N17" s="10"/>
       <c r="T17" s="10"/>
       <c r="V17" s="10" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="W17" s="10" t="s">
         <v>117</v>
@@ -4012,7 +4013,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>17</v>
       </c>
@@ -4051,7 +4052,7 @@
       <c r="N18" s="10"/>
       <c r="T18" s="10"/>
       <c r="V18" s="10" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="W18" s="10" t="s">
         <v>117</v>
@@ -4066,7 +4067,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>18</v>
       </c>
@@ -4105,7 +4106,7 @@
       <c r="N19" s="10"/>
       <c r="T19" s="10"/>
       <c r="V19" s="10" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="W19" s="10" t="s">
         <v>117</v>
@@ -4120,7 +4121,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="150" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="145" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>19</v>
       </c>
@@ -4174,16 +4175,16 @@
         <v>164</v>
       </c>
       <c r="AB20" s="14" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AD20" s="9" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>20</v>
       </c>
@@ -4215,13 +4216,13 @@
         <v>170</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="T21" s="10"/>
       <c r="W21" s="14" t="s">
@@ -4240,16 +4241,16 @@
         <v>172</v>
       </c>
       <c r="AB21" s="14" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AD21" s="9" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>21</v>
       </c>
@@ -4294,7 +4295,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="120" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="116" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>22</v>
       </c>
@@ -4320,19 +4321,19 @@
       <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23" s="14" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="P23" s="10" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="V23" s="14" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="W23" s="14" t="s">
         <v>171</v>
@@ -4350,16 +4351,16 @@
         <v>181</v>
       </c>
       <c r="AB23" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AC23" s="10" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="AD23" s="10" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" ht="150" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="145" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>23</v>
       </c>
@@ -4410,7 +4411,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>24</v>
       </c>
@@ -4462,7 +4463,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A26" s="9">
         <v>25</v>
       </c>
@@ -4514,16 +4515,16 @@
         <v>202</v>
       </c>
       <c r="AB26" s="14" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="AC26" s="10" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="AD26" s="9" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
         <v>26</v>
       </c>
@@ -4574,7 +4575,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="9">
         <v>27</v>
       </c>
@@ -4619,7 +4620,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="9">
         <v>28</v>
       </c>
@@ -4670,7 +4671,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="9">
         <v>29</v>
       </c>
@@ -4715,7 +4716,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" s="9">
         <v>30</v>
       </c>
@@ -4766,7 +4767,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="9">
         <v>31</v>
       </c>
@@ -4820,7 +4821,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="9">
         <v>32</v>
       </c>
@@ -4865,7 +4866,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34" s="9">
         <v>33</v>
       </c>
@@ -4912,7 +4913,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
         <v>34</v>
       </c>
@@ -4957,7 +4958,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="9">
         <v>35</v>
       </c>
@@ -5013,7 +5014,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A37" s="9">
         <v>36</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="9">
         <v>37</v>
       </c>
@@ -5121,7 +5122,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
         <v>38</v>
       </c>
@@ -5175,7 +5176,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A40" s="9">
         <v>39</v>
       </c>
@@ -5220,7 +5221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="58" x14ac:dyDescent="0.35">
       <c r="A41" s="9">
         <v>40</v>
       </c>
@@ -5268,10 +5269,10 @@
         <v>290</v>
       </c>
       <c r="AC41" s="10" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A42" s="9">
         <v>41</v>
       </c>
@@ -5318,7 +5319,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
         <v>42</v>
       </c>
@@ -5365,7 +5366,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A44" s="9">
         <v>43</v>
       </c>
@@ -5412,7 +5413,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A45" s="9">
         <v>44</v>
       </c>
@@ -5459,7 +5460,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="60" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="58" x14ac:dyDescent="0.35">
       <c r="A46" s="9">
         <v>45</v>
       </c>
@@ -5511,7 +5512,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A47" s="9">
         <v>46</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
         <v>47</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="9">
         <v>48</v>
       </c>
@@ -5663,7 +5664,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A50" s="9">
         <v>49</v>
       </c>
@@ -5713,10 +5714,10 @@
         <v>341</v>
       </c>
       <c r="AC50" s="10" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="51" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="9">
         <v>50</v>
       </c>
@@ -5772,7 +5773,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="9">
         <v>51</v>
       </c>
@@ -5821,7 +5822,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
         <v>52</v>
       </c>
@@ -5873,7 +5874,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="9">
         <v>53</v>
       </c>
@@ -5923,16 +5924,16 @@
         <v>96</v>
       </c>
       <c r="Z54" s="12" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="AA54" s="10" t="s">
         <v>327</v>
       </c>
       <c r="AC54" s="10" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="55" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A55" s="9">
         <v>54</v>
       </c>
@@ -5963,13 +5964,13 @@
         <v>370</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="T55" s="10" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="V55" s="10" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="W55" s="10" t="s">
         <v>117</v>
@@ -5987,10 +5988,10 @@
         <v>371</v>
       </c>
       <c r="AC55" s="10" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="56" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
         <v>55</v>
       </c>
@@ -6043,13 +6044,13 @@
         <v>380</v>
       </c>
       <c r="AB56" s="14" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="AD56" s="9" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="57" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="9">
         <v>56</v>
       </c>
@@ -6079,14 +6080,14 @@
         <v>383</v>
       </c>
       <c r="M57" s="10" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="T57" s="10"/>
       <c r="V57" s="10" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="W57" s="10" t="s">
         <v>117</v>
@@ -6104,10 +6105,10 @@
         <v>384</v>
       </c>
       <c r="AC57" s="10" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="58" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="9">
         <v>57</v>
       </c>
@@ -6156,16 +6157,16 @@
         <v>171</v>
       </c>
       <c r="AB58" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AC58" s="10" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="AD58" s="9" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A59" s="9">
         <v>58</v>
       </c>
@@ -6210,7 +6211,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="135" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9">
         <v>59</v>
       </c>
@@ -6257,7 +6258,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
         <v>60</v>
       </c>
@@ -6304,7 +6305,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="9">
         <v>61</v>
       </c>
@@ -6351,7 +6352,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="63" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A63" s="9">
         <v>62</v>
       </c>
@@ -6396,7 +6397,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="64" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A64" s="9">
         <v>63</v>
       </c>
@@ -6441,7 +6442,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="65" spans="1:30" ht="165" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A65" s="9">
         <v>64</v>
       </c>
@@ -6486,7 +6487,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A66" s="9">
         <v>65</v>
       </c>
@@ -6533,7 +6534,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="67" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="9">
         <v>66</v>
       </c>
@@ -6580,7 +6581,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A68" s="9">
         <v>67</v>
       </c>
@@ -6627,7 +6628,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:30" ht="90" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="87" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
         <v>68</v>
       </c>
@@ -6672,7 +6673,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="70" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A70" s="9">
         <v>69</v>
       </c>
@@ -6705,10 +6706,10 @@
         <v>429</v>
       </c>
       <c r="N70" s="10" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="P70" s="10" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="S70" s="16"/>
       <c r="T70" s="14"/>
@@ -6728,16 +6729,16 @@
         <v>430</v>
       </c>
       <c r="AB70" s="14" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="AC70" s="10" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="AD70" s="10" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="71" spans="1:30" ht="90" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="71" spans="1:30" ht="87" x14ac:dyDescent="0.35">
       <c r="A71" s="9">
         <v>70</v>
       </c>
@@ -6784,7 +6785,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="72" spans="1:30" ht="180" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="174" x14ac:dyDescent="0.35">
       <c r="A72" s="9">
         <v>71</v>
       </c>
@@ -6816,16 +6817,16 @@
         <v>101</v>
       </c>
       <c r="M72" s="14" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="N72" s="10" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="P72" s="10" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="T72" s="10" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="V72" s="14"/>
       <c r="W72" s="14" t="s">
@@ -6844,16 +6845,16 @@
         <v>439</v>
       </c>
       <c r="AB72" s="14" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="AC72" s="10" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="AD72" s="10" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="73" spans="1:30" ht="30" x14ac:dyDescent="0.25">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="9">
         <v>72</v>
       </c>
@@ -6900,7 +6901,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="74" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
         <v>73</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="75" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A75" s="9">
         <v>74</v>
       </c>
@@ -6999,13 +7000,13 @@
         <v>458</v>
       </c>
       <c r="Z75" s="11" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="AC75" s="10" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="76" spans="1:30" ht="409.5" x14ac:dyDescent="0.25">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="76" spans="1:30" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A76" s="9">
         <v>75</v>
       </c>
@@ -7049,13 +7050,13 @@
         <v>458</v>
       </c>
       <c r="Z76" s="11" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="AC76" s="10" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="77" spans="1:30" ht="90" x14ac:dyDescent="0.25">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="77" spans="1:30" ht="87" x14ac:dyDescent="0.35">
       <c r="A77" s="9">
         <v>76</v>
       </c>
@@ -7106,7 +7107,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="78" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78" s="9">
         <v>77</v>
       </c>
@@ -7141,10 +7142,10 @@
         <v>476</v>
       </c>
       <c r="N78" s="10" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="T78" s="10" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="W78" s="10" t="s">
         <v>38</v>
@@ -7162,10 +7163,10 @@
         <v>478</v>
       </c>
       <c r="AD78" s="9" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="79" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="79" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A79" s="9">
         <v>78</v>
       </c>
@@ -7217,13 +7218,13 @@
         <v>484</v>
       </c>
       <c r="AB79" s="14" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AD79" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="80" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="80" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A80" s="9">
         <v>79</v>
       </c>
@@ -7279,13 +7280,13 @@
         <v>491</v>
       </c>
       <c r="AB80" s="14" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AD80" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="81" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="81" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A81" s="9">
         <v>80</v>
       </c>
@@ -7341,13 +7342,13 @@
         <v>498</v>
       </c>
       <c r="AB81" s="14" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AD81" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="82" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="82" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A82" s="9">
         <v>81</v>
       </c>
@@ -7403,13 +7404,13 @@
         <v>504</v>
       </c>
       <c r="AB82" s="14" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="AD82" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="83" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="83" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
         <v>82</v>
       </c>
@@ -7458,7 +7459,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="9">
         <v>83</v>
       </c>
@@ -7490,28 +7491,34 @@
         <v>475</v>
       </c>
       <c r="M84" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="N84" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="N84" s="10" t="s">
+      <c r="T84" s="10" t="s">
         <v>514</v>
       </c>
-      <c r="T84" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="W84" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="X84" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y84" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z84" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+      <c r="W84" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X84" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y84" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z84" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC84" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="AD84" s="9" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="85" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="9">
         <v>84</v>
       </c>
@@ -7519,13 +7526,13 @@
         <v>32</v>
       </c>
       <c r="C85" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="D85" s="7" t="s">
+      <c r="E85" s="7" t="s">
         <v>517</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>518</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>55</v>
@@ -7533,13 +7540,13 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="J85" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="J85" s="7" t="s">
+      <c r="K85" s="7" t="s">
         <v>520</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>521</v>
       </c>
       <c r="L85" s="8" t="s">
         <v>475</v>
@@ -7562,13 +7569,13 @@
         <v>171</v>
       </c>
       <c r="AB85" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AD85" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="86" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="86" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
         <v>85</v>
       </c>
@@ -7576,13 +7583,13 @@
         <v>32</v>
       </c>
       <c r="C86" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="D86" s="7" t="s">
+      <c r="E86" s="7" t="s">
         <v>523</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>524</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>55</v>
@@ -7590,10 +7597,10 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J86" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="8" t="s">
@@ -7603,34 +7610,34 @@
         <v>45</v>
       </c>
       <c r="N86" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="T86" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="T86" s="10" t="s">
+      <c r="W86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z86" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AA86" s="10" t="s">
         <v>527</v>
       </c>
-      <c r="W86" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="X86" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y86" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="Z86" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA86" s="10" t="s">
-        <v>528</v>
-      </c>
       <c r="AB86" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AD86" s="10" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="87" spans="1:30" ht="90" x14ac:dyDescent="0.25">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="87" spans="1:30" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A87" s="9">
         <v>86</v>
       </c>
@@ -7638,13 +7645,13 @@
         <v>32</v>
       </c>
       <c r="C87" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="E87" s="7" t="s">
         <v>530</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>531</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>55</v>
@@ -7653,38 +7660,41 @@
       <c r="H87" s="7"/>
       <c r="I87" s="7"/>
       <c r="J87" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="M87" s="10" t="s">
+      <c r="N87" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="T87" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="N87" s="10" t="s">
+      <c r="V87" s="10" t="s">
         <v>534</v>
       </c>
-      <c r="T87" s="10" t="s">
-        <v>535</v>
-      </c>
-      <c r="V87" s="10" t="s">
-        <v>536</v>
-      </c>
-      <c r="W87" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="X87" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y87" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z87" s="11" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="88" spans="1:30" ht="105" x14ac:dyDescent="0.25">
+      <c r="W87" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="X87" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y87" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Z87" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AC87" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="AD87" s="9" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="88" spans="1:30" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A88" s="9">
         <v>87</v>
       </c>
@@ -7692,13 +7702,13 @@
         <v>32</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>55</v>
@@ -7706,25 +7716,25 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="7" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J88" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K88" s="7" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="L88" s="8" t="s">
         <v>475</v>
       </c>
       <c r="M88" s="10" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="N88" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="T88" s="10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="W88" s="10" t="s">
         <v>38</v>
@@ -7736,10 +7746,10 @@
         <v>76</v>
       </c>
       <c r="Z88" s="11" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="89" spans="1:30" ht="105" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="89" spans="1:30" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A89" s="9">
         <v>88</v>
       </c>
@@ -7747,13 +7757,13 @@
         <v>32</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>55</v>
@@ -7763,19 +7773,19 @@
       <c r="I89" s="7"/>
       <c r="J89" s="7"/>
       <c r="K89" s="7" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="L89" s="8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M89" s="10" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="T89" s="10" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="W89" s="10" t="s">
         <v>38</v>
@@ -7787,10 +7797,10 @@
         <v>76</v>
       </c>
       <c r="Z89" s="11" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="90" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A90" s="9">
         <v>89</v>
       </c>
@@ -7798,13 +7808,13 @@
         <v>32</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>55</v>
@@ -7813,10 +7823,10 @@
       <c r="H90" s="7"/>
       <c r="I90" s="7"/>
       <c r="J90" s="7" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L90" s="8" t="s">
         <v>475</v>
@@ -7825,10 +7835,10 @@
         <v>45</v>
       </c>
       <c r="N90" s="10" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="T90" s="10" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="W90" s="14" t="s">
         <v>171</v>
@@ -7843,16 +7853,16 @@
         <v>171</v>
       </c>
       <c r="AA90" s="10" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="AB90" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AD90" s="9" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="91" spans="1:30" ht="60" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="91" spans="1:30" ht="58" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
         <v>90</v>
       </c>
@@ -7860,13 +7870,13 @@
         <v>32</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>55</v>
@@ -7875,7 +7885,7 @@
       <c r="H91" s="7"/>
       <c r="I91" s="7"/>
       <c r="J91" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="8" t="s">
@@ -7899,19 +7909,19 @@
         <v>171</v>
       </c>
       <c r="AA91" s="10" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AB91" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AC91" s="10" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="AD91" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="92" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="92" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A92" s="9">
         <v>91</v>
       </c>
@@ -7919,13 +7929,13 @@
         <v>32</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>55</v>
@@ -7934,7 +7944,7 @@
       <c r="H92" s="7"/>
       <c r="I92" s="7"/>
       <c r="J92" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="8" t="s">
@@ -7958,13 +7968,13 @@
         <v>171</v>
       </c>
       <c r="AB92" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD92" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="93" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="93" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A93" s="9">
         <v>92</v>
       </c>
@@ -7972,13 +7982,13 @@
         <v>32</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>55</v>
@@ -7987,7 +7997,7 @@
       <c r="H93" s="7"/>
       <c r="I93" s="7"/>
       <c r="J93" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="8" t="s">
@@ -8011,13 +8021,13 @@
         <v>171</v>
       </c>
       <c r="AB93" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD93" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="94" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="94" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A94" s="9">
         <v>93</v>
       </c>
@@ -8025,13 +8035,13 @@
         <v>32</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D94" s="7" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>55</v>
@@ -8040,7 +8050,7 @@
       <c r="H94" s="7"/>
       <c r="I94" s="7"/>
       <c r="J94" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="8" t="s">
@@ -8064,13 +8074,13 @@
         <v>171</v>
       </c>
       <c r="AB94" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD94" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="95" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A95" s="9">
         <v>94</v>
       </c>
@@ -8078,13 +8088,13 @@
         <v>32</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>55</v>
@@ -8093,7 +8103,7 @@
       <c r="H95" s="7"/>
       <c r="I95" s="7"/>
       <c r="J95" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="8" t="s">
@@ -8117,13 +8127,13 @@
         <v>171</v>
       </c>
       <c r="AB95" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD95" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="96" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="96" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
         <v>95</v>
       </c>
@@ -8131,13 +8141,13 @@
         <v>32</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>55</v>
@@ -8146,7 +8156,7 @@
       <c r="H96" s="7"/>
       <c r="I96" s="7"/>
       <c r="J96" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="8" t="s">
@@ -8170,13 +8180,13 @@
         <v>171</v>
       </c>
       <c r="AB96" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD96" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="97" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" s="9">
         <v>96</v>
       </c>
@@ -8184,13 +8194,13 @@
         <v>32</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>55</v>
@@ -8199,7 +8209,7 @@
       <c r="H97" s="7"/>
       <c r="I97" s="7"/>
       <c r="J97" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="8" t="s">
@@ -8223,13 +8233,13 @@
         <v>171</v>
       </c>
       <c r="AB97" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD97" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="98" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="9">
         <v>97</v>
       </c>
@@ -8237,13 +8247,13 @@
         <v>32</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>55</v>
@@ -8252,7 +8262,7 @@
       <c r="H98" s="7"/>
       <c r="I98" s="7"/>
       <c r="J98" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="8" t="s">
@@ -8276,13 +8286,13 @@
         <v>171</v>
       </c>
       <c r="AB98" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD98" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="99" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A99" s="9">
         <v>98</v>
       </c>
@@ -8290,13 +8300,13 @@
         <v>32</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>55</v>
@@ -8305,7 +8315,7 @@
       <c r="H99" s="7"/>
       <c r="I99" s="7"/>
       <c r="J99" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="8" t="s">
@@ -8329,13 +8339,13 @@
         <v>171</v>
       </c>
       <c r="AB99" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD99" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="100" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A100" s="9">
         <v>99</v>
       </c>
@@ -8343,13 +8353,13 @@
         <v>32</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>55</v>
@@ -8358,7 +8368,7 @@
       <c r="H100" s="7"/>
       <c r="I100" s="7"/>
       <c r="J100" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="8" t="s">
@@ -8382,13 +8392,13 @@
         <v>171</v>
       </c>
       <c r="AB100" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD100" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="101" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A101" s="9">
         <v>100</v>
       </c>
@@ -8396,13 +8406,13 @@
         <v>32</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>55</v>
@@ -8411,7 +8421,7 @@
       <c r="H101" s="7"/>
       <c r="I101" s="7"/>
       <c r="J101" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="8" t="s">
@@ -8421,10 +8431,10 @@
         <v>45</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T101" s="10" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="W101" s="14" t="s">
         <v>171</v>
@@ -8439,16 +8449,16 @@
         <v>171</v>
       </c>
       <c r="AA101" s="10" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="AB101" s="14" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="AD101" s="9" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="102" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A102" s="9">
         <v>101</v>
       </c>
@@ -8456,13 +8466,13 @@
         <v>32</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>55</v>
@@ -8471,7 +8481,7 @@
       <c r="H102" s="7"/>
       <c r="I102" s="7"/>
       <c r="J102" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="8" t="s">
@@ -8495,13 +8505,13 @@
         <v>171</v>
       </c>
       <c r="AB102" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD102" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="103" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="103" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A103" s="9">
         <v>102</v>
       </c>
@@ -8509,13 +8519,13 @@
         <v>32</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>55</v>
@@ -8524,7 +8534,7 @@
       <c r="H103" s="7"/>
       <c r="I103" s="7"/>
       <c r="J103" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="8" t="s">
@@ -8548,13 +8558,13 @@
         <v>171</v>
       </c>
       <c r="AB103" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD103" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="104" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A104" s="9">
         <v>103</v>
       </c>
@@ -8562,13 +8572,13 @@
         <v>32</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>55</v>
@@ -8577,7 +8587,7 @@
       <c r="H104" s="7"/>
       <c r="I104" s="7"/>
       <c r="J104" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="8" t="s">
@@ -8601,13 +8611,13 @@
         <v>171</v>
       </c>
       <c r="AB104" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD104" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="105" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A105" s="9">
         <v>104</v>
       </c>
@@ -8615,13 +8625,13 @@
         <v>32</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>55</v>
@@ -8630,7 +8640,7 @@
       <c r="H105" s="7"/>
       <c r="I105" s="7"/>
       <c r="J105" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="8" t="s">
@@ -8654,13 +8664,13 @@
         <v>171</v>
       </c>
       <c r="AB105" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD105" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="106" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="9">
         <v>105</v>
       </c>
@@ -8668,13 +8678,13 @@
         <v>32</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>55</v>
@@ -8683,7 +8693,7 @@
       <c r="H106" s="7"/>
       <c r="I106" s="7"/>
       <c r="J106" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="8" t="s">
@@ -8707,13 +8717,13 @@
         <v>171</v>
       </c>
       <c r="AB106" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD106" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="107" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" s="9">
         <v>106</v>
       </c>
@@ -8721,13 +8731,13 @@
         <v>32</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>55</v>
@@ -8736,7 +8746,7 @@
       <c r="H107" s="7"/>
       <c r="I107" s="7"/>
       <c r="J107" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="8" t="s">
@@ -8760,13 +8770,13 @@
         <v>171</v>
       </c>
       <c r="AB107" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD107" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="108" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
         <v>107</v>
       </c>
@@ -8774,13 +8784,13 @@
         <v>32</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>55</v>
@@ -8789,7 +8799,7 @@
       <c r="H108" s="7"/>
       <c r="I108" s="7"/>
       <c r="J108" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="8" t="s">
@@ -8813,13 +8823,13 @@
         <v>171</v>
       </c>
       <c r="AB108" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD108" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="109" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A109" s="9">
         <v>108</v>
       </c>
@@ -8827,13 +8837,13 @@
         <v>32</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D109" s="7" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>55</v>
@@ -8842,7 +8852,7 @@
       <c r="H109" s="7"/>
       <c r="I109" s="7"/>
       <c r="J109" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="8" t="s">
@@ -8866,13 +8876,13 @@
         <v>171</v>
       </c>
       <c r="AB109" s="14" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="AD109" s="10" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="110" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A110" s="9">
         <v>109</v>
       </c>
@@ -8880,13 +8890,13 @@
         <v>32</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>55</v>
@@ -8895,7 +8905,7 @@
       <c r="H110" s="7"/>
       <c r="I110" s="7"/>
       <c r="J110" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="8" t="s">
@@ -8919,7 +8929,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="111" spans="1:30" ht="75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A111" s="9">
         <v>110</v>
       </c>
@@ -8927,13 +8937,13 @@
         <v>32</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D111" s="7" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>55</v>
@@ -8942,7 +8952,7 @@
       <c r="H111" s="7"/>
       <c r="I111" s="7"/>
       <c r="J111" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="8" t="s">
@@ -8952,10 +8962,10 @@
         <v>45</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="T111" s="10"/>
       <c r="W111" s="14" t="s">
@@ -8971,13 +8981,13 @@
         <v>117</v>
       </c>
       <c r="AA111" s="10" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="AC111" s="14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="112" spans="1:30" ht="45" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A112" s="9">
         <v>111</v>
       </c>
@@ -8985,13 +8995,13 @@
         <v>32</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>55</v>
@@ -9000,7 +9010,7 @@
       <c r="H112" s="7"/>
       <c r="I112" s="7"/>
       <c r="J112" s="7" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="8" t="s">
@@ -9024,7 +9034,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="9">
         <v>112</v>
       </c>
@@ -9032,13 +9042,13 @@
         <v>32</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>55</v>
@@ -9047,20 +9057,20 @@
       <c r="H113" s="7"/>
       <c r="I113" s="7"/>
       <c r="J113" s="7" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="8" t="s">
         <v>475</v>
       </c>
       <c r="M113" s="10" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="T113" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="W113" s="10" t="s">
         <v>38</v>
@@ -9075,7 +9085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A114" s="9">
         <v>113</v>
       </c>
@@ -9083,13 +9093,13 @@
         <v>32</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>55</v>
@@ -9098,20 +9108,20 @@
       <c r="H114" s="7"/>
       <c r="I114" s="7"/>
       <c r="J114" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="8" t="s">
         <v>475</v>
       </c>
       <c r="M114" s="10" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N114" s="10" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="T114" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="W114" s="10" t="s">
         <v>38</v>
@@ -9126,7 +9136,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:27" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A115" s="9">
         <v>114</v>
       </c>
@@ -9134,13 +9144,13 @@
         <v>32</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>55</v>
@@ -9149,20 +9159,20 @@
       <c r="H115" s="7"/>
       <c r="I115" s="7"/>
       <c r="J115" s="7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="8" t="s">
         <v>475</v>
       </c>
       <c r="M115" s="10" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="T115" s="10" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="W115" s="10" t="s">
         <v>38</v>
@@ -9177,7 +9187,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A116" s="9">
         <v>115</v>
       </c>
@@ -9185,13 +9195,13 @@
         <v>32</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>55</v>
@@ -9200,7 +9210,7 @@
       <c r="H116" s="7"/>
       <c r="I116" s="7"/>
       <c r="J116" s="7" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="8"/>
@@ -9222,7 +9232,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A117" s="9">
         <v>116</v>
       </c>
@@ -9230,13 +9240,13 @@
         <v>32</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>55</v>
@@ -9245,7 +9255,7 @@
       <c r="H117" s="7"/>
       <c r="I117" s="7"/>
       <c r="J117" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="8"/>
@@ -9267,7 +9277,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
         <v>117</v>
       </c>
@@ -9275,13 +9285,13 @@
         <v>32</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>55</v>
@@ -9290,7 +9300,7 @@
       <c r="H118" s="7"/>
       <c r="I118" s="7"/>
       <c r="J118" s="7" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="8"/>
@@ -9312,7 +9322,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A119" s="9">
         <v>118</v>
       </c>
@@ -9320,13 +9330,13 @@
         <v>32</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>55</v>
@@ -9335,7 +9345,7 @@
       <c r="H119" s="7"/>
       <c r="I119" s="7"/>
       <c r="J119" s="7" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="8"/>
@@ -9357,7 +9367,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="375" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:27" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A120" s="9">
         <v>119</v>
       </c>
@@ -9365,13 +9375,13 @@
         <v>32</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>55</v>
@@ -9380,18 +9390,18 @@
       <c r="H120" s="7"/>
       <c r="I120" s="7"/>
       <c r="J120" s="7" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="8"/>
       <c r="M120" s="10" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="N120" s="10" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="T120" s="10" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="W120" s="10" t="s">
         <v>38</v>
@@ -9403,13 +9413,13 @@
         <v>458</v>
       </c>
       <c r="Z120" s="12" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="AA120" s="10" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.25">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A121" s="9">
         <v>120</v>
       </c>
@@ -9417,13 +9427,13 @@
         <v>32</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>55</v>
@@ -9432,7 +9442,7 @@
       <c r="H121" s="7"/>
       <c r="I121" s="7"/>
       <c r="J121" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="8"/>
@@ -9454,7 +9464,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
         <v>121</v>
       </c>
@@ -9462,13 +9472,13 @@
         <v>32</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>55</v>
@@ -9477,7 +9487,7 @@
       <c r="H122" s="7"/>
       <c r="I122" s="7"/>
       <c r="J122" s="7" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="8"/>
